--- a/faire_template.xlsx
+++ b/faire_template.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10503"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zalmanek/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0C14403-42BB-5148-9477-4888D6FAD9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
+    <workbookView xWindow="1200" yWindow="1840" windowWidth="27900" windowHeight="18340" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="README"/>
-    <sheet r:id="rId2" sheetId="2" name="projectMetadata"/>
-    <sheet r:id="rId3" sheetId="3" name="analysisMetadata"/>
-    <sheet r:id="rId4" sheetId="4" name="sampleMetadata"/>
-    <sheet r:id="rId5" sheetId="5" name="Drop-down values"/>
-    <sheet r:id="rId6" sheetId="6" name="experimentRunMetadata"/>
+    <sheet name="README" sheetId="1" r:id="rId1"/>
+    <sheet name="projectMetadata" sheetId="2" r:id="rId2"/>
+    <sheet name="analysisMetadata" sheetId="3" r:id="rId3"/>
+    <sheet name="sampleMetadata" sheetId="4" r:id="rId4"/>
+    <sheet name="Drop-down values" sheetId="5" r:id="rId5"/>
+    <sheet name="experimentRunMetadata" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1578,9 +1584,6 @@
     <t>qiime2_version</t>
   </si>
   <si>
-    <t>tourmaline_asv_method</t>
-  </si>
-  <si>
     <t>dada2_trunc_len_f</t>
   </si>
   <si>
@@ -2044,13 +2047,15 @@
   </si>
   <si>
     <t>11. Please don't hesitate to reach out to us with questions or concerns: bayden.willms@noaa.gov</t>
+  </si>
+  <si>
+    <t>asv_method</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2082,22 +2087,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe26b0a"/>
+        <fgColor rgb="FFE26B0A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffff99"/>
+        <fgColor rgb="FFFFFF99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFccff99"/>
+        <fgColor rgb="FFCCFF99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffcc00"/>
+        <fgColor rgb="FFFFCC00"/>
       </patternFill>
     </fill>
   </fills>
@@ -2118,16 +2123,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2135,56 +2140,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2195,10 +2197,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -2236,71 +2238,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2328,7 +2330,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2351,11 +2353,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -2364,13 +2366,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2380,7 +2382,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -2389,7 +2391,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -2398,7 +2400,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -2406,10 +2408,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -2474,319 +2476,241 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="3" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="15.75">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="15.75">
-      <c r="A2" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="15.75">
-      <c r="A3" s="1"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="15.75">
-      <c r="A4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="15.75">
-      <c r="A5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="15.75">
-      <c r="A6" s="1"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="15.75">
-      <c r="A7" s="5" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="15.75">
-      <c r="A8" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="C8" s="5" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>641</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="15.75">
-      <c r="A9" s="1" t="s">
-        <v>642</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="15.75">
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="15.75">
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="15.75">
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="15.75">
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="15.75">
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="15.75">
-      <c r="A15" s="5" t="s">
+    </row>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="15.75">
-      <c r="A16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="15.75">
-      <c r="A17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="15.75">
-      <c r="A18" s="1" t="s">
+    </row>
+    <row r="19" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="15.75">
-      <c r="A19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="15.75">
-      <c r="A20" s="1"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="15.75">
-      <c r="A21" s="5" t="s">
+    </row>
+    <row r="22" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
         <v>652</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="15.75">
-      <c r="A22" s="13" t="s">
+    </row>
+    <row r="23" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="15.75">
-      <c r="A23" s="11" t="s">
+    </row>
+    <row r="24" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="15.75">
-      <c r="A24" s="3" t="s">
+    </row>
+    <row r="25" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="15.75">
-      <c r="A25" s="4" t="s">
+    </row>
+    <row r="26" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="4"/>
+    </row>
+    <row r="27" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
         <v>656</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="15.75">
-      <c r="A26" s="4"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="15.75">
-      <c r="A27" s="5" t="s">
+    </row>
+    <row r="28" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
         <v>657</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="15.75">
-      <c r="A28" s="5" t="s">
+    </row>
+    <row r="29" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="15.75">
-      <c r="A29" s="1" t="s">
+    </row>
+    <row r="30" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="15.75">
-      <c r="A30" s="1" t="s">
+    </row>
+    <row r="31" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="15.75">
-      <c r="A31" s="1" t="s">
+    </row>
+    <row r="32" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="15.75">
-      <c r="A32" s="1" t="s">
+    </row>
+    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="15.75">
-      <c r="A33" s="1" t="s">
+    </row>
+    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="15.75">
-      <c r="A34" s="1" t="s">
+    </row>
+    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="15.75">
-      <c r="A35" s="1" t="s">
+    </row>
+    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="15.75">
-      <c r="A36" s="1" t="s">
+    </row>
+    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="15.75">
-      <c r="A37" s="1" t="s">
+    </row>
+    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="15.75">
-      <c r="A38" s="1" t="s">
+    </row>
+    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="15.75">
-      <c r="A39" s="1" t="s">
+    </row>
+    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="15.75">
-      <c r="A40" s="1" t="s">
+    </row>
+    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="15.75">
-      <c r="A41" s="1" t="s">
+    </row>
+    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="15.75">
-      <c r="A42" s="1" t="s">
+    </row>
+    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="15.75">
-      <c r="A43" s="1" t="s">
+    </row>
+    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="15.75">
-      <c r="A44" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2794,37 +2718,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:S101"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="19" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="15.75">
+    <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>475</v>
@@ -2833,37 +2739,37 @@
         <v>25</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>555</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>556</v>
       </c>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
@@ -2871,7 +2777,7 @@
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="15.75">
+    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2879,7 +2785,7 @@
         <v>477</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -2892,13 +2798,8 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="15.75">
+    </row>
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2906,7 +2807,7 @@
         <v>477</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -2919,13 +2820,8 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="15.75">
+    </row>
+    <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -2933,7 +2829,7 @@
         <v>477</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -2946,13 +2842,8 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="15.75">
+    </row>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2960,7 +2851,7 @@
         <v>477</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -2973,13 +2864,8 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="15.75">
+    </row>
+    <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -2987,7 +2873,7 @@
         <v>477</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -3000,13 +2886,8 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="15.75">
+    </row>
+    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -3014,7 +2895,7 @@
         <v>477</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -3027,13 +2908,8 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="15.75">
+    </row>
+    <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
@@ -3056,13 +2932,8 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="15.75">
+    </row>
+    <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>3</v>
       </c>
@@ -3070,7 +2941,7 @@
         <v>477</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -3083,13 +2954,8 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="15.75">
+    </row>
+    <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
@@ -3097,7 +2963,7 @@
         <v>477</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -3110,13 +2976,8 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="15.75">
+    </row>
+    <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
@@ -3139,21 +3000,16 @@
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="15.75">
-      <c r="A12" s="11" t="s">
+    </row>
+    <row r="12" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>477</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -3166,14 +3022,9 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="15.75">
-      <c r="A13" s="11" t="s">
+    </row>
+    <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -3193,14 +3044,9 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="15.75">
-      <c r="A14" s="11" t="s">
+    </row>
+    <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -3220,13 +3066,8 @@
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="15.75">
+    </row>
+    <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
@@ -3234,10 +3075,10 @@
         <v>346</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>566</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>567</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -3249,13 +3090,8 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="15.75">
+    </row>
+    <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>2</v>
       </c>
@@ -3263,7 +3099,7 @@
         <v>346</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -3276,13 +3112,8 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="15.75">
+    </row>
+    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
@@ -3290,7 +3121,7 @@
         <v>346</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -3303,13 +3134,8 @@
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="15.75">
+    </row>
+    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>2</v>
       </c>
@@ -3317,7 +3143,7 @@
         <v>346</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -3330,13 +3156,8 @@
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="15.75">
+    </row>
+    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>2</v>
       </c>
@@ -3344,7 +3165,7 @@
         <v>346</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -3357,13 +3178,8 @@
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="15.75">
+    </row>
+    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>3</v>
       </c>
@@ -3371,7 +3187,7 @@
         <v>346</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -3384,13 +3200,8 @@
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="15.75">
+    </row>
+    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>3</v>
       </c>
@@ -3398,7 +3209,7 @@
         <v>346</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -3411,13 +3222,8 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="15.75">
+    </row>
+    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>2</v>
       </c>
@@ -3425,7 +3231,7 @@
         <v>346</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -3438,13 +3244,8 @@
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="15.75">
+    </row>
+    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>3</v>
       </c>
@@ -3452,7 +3253,7 @@
         <v>346</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -3465,13 +3266,8 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
-      <c r="S23" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="15.75">
+    </row>
+    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>2</v>
       </c>
@@ -3479,7 +3275,7 @@
         <v>346</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -3492,13 +3288,8 @@
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="15.75">
+    </row>
+    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>2</v>
       </c>
@@ -3506,7 +3297,7 @@
         <v>341</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -3519,13 +3310,8 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="15.75">
+    </row>
+    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>1</v>
       </c>
@@ -3546,13 +3332,8 @@
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="15.75">
+    </row>
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>3</v>
       </c>
@@ -3573,13 +3354,8 @@
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
-      <c r="S27" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="15.75">
+    </row>
+    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>3</v>
       </c>
@@ -3587,7 +3363,7 @@
         <v>5</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -3600,13 +3376,8 @@
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="15.75">
+    </row>
+    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>3</v>
       </c>
@@ -3614,7 +3385,7 @@
         <v>5</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -3627,13 +3398,8 @@
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="15.75">
+    </row>
+    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>1</v>
       </c>
@@ -3643,24 +3409,8 @@
       <c r="C30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="15.75">
+    </row>
+    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>2</v>
       </c>
@@ -3668,7 +3418,7 @@
         <v>5</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -3681,13 +3431,8 @@
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="6"/>
-      <c r="S31" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="15.75">
+    </row>
+    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>1</v>
       </c>
@@ -3695,7 +3440,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -3708,13 +3453,8 @@
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="15.75">
+    </row>
+    <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>2</v>
       </c>
@@ -3722,7 +3462,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -3735,14 +3475,9 @@
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="6"/>
-      <c r="S33" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="15.75">
-      <c r="A34" s="11" t="s">
+    </row>
+    <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -3762,13 +3497,8 @@
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="6"/>
-      <c r="S34" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="15.75">
+    </row>
+    <row r="35" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>3</v>
       </c>
@@ -3776,7 +3506,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -3789,21 +3519,16 @@
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
-      <c r="O35" s="6"/>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="6"/>
-      <c r="S35" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="15.75">
-      <c r="A36" s="11" t="s">
+    </row>
+    <row r="36" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -3816,13 +3541,8 @@
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="15.75">
+    </row>
+    <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>1</v>
       </c>
@@ -3830,7 +3550,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -3843,13 +3563,8 @@
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="6"/>
-      <c r="S37" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="15.75">
+    </row>
+    <row r="38" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>1</v>
       </c>
@@ -3857,7 +3572,7 @@
         <v>5</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -3870,13 +3585,8 @@
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
-      <c r="S38" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="15.75">
+    </row>
+    <row r="39" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>2</v>
       </c>
@@ -3884,7 +3594,7 @@
         <v>5</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -3897,13 +3607,8 @@
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
-      <c r="S39" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="15.75">
+    </row>
+    <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>2</v>
       </c>
@@ -3911,7 +3616,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -3924,21 +3629,16 @@
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
-      <c r="O40" s="6"/>
-      <c r="P40" s="6"/>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="15.75">
-      <c r="A41" s="11" t="s">
+    </row>
+    <row r="41" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -3951,21 +3651,16 @@
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
-      <c r="O41" s="6"/>
-      <c r="P41" s="6"/>
-      <c r="Q41" s="6"/>
-      <c r="R41" s="6"/>
-      <c r="S41" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="15.75">
-      <c r="A42" s="11" t="s">
+    </row>
+    <row r="42" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -3978,13 +3673,8 @@
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="6"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="6"/>
-      <c r="S42" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="15.75">
+    </row>
+    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>2</v>
       </c>
@@ -3992,7 +3682,7 @@
         <v>5</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -4005,13 +3695,8 @@
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="6"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="6"/>
-      <c r="S43" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="15.75">
+    </row>
+    <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>2</v>
       </c>
@@ -4019,7 +3704,7 @@
         <v>5</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -4032,13 +3717,8 @@
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
-      <c r="O44" s="6"/>
-      <c r="P44" s="6"/>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="6"/>
-      <c r="S44" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="15.75">
+    </row>
+    <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>2</v>
       </c>
@@ -4046,7 +3726,7 @@
         <v>5</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -4059,13 +3739,8 @@
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="6"/>
-      <c r="Q45" s="6"/>
-      <c r="R45" s="6"/>
-      <c r="S45" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="15.75">
+    </row>
+    <row r="46" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>2</v>
       </c>
@@ -4073,7 +3748,7 @@
         <v>5</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -4086,21 +3761,16 @@
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="6"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="15.75">
-      <c r="A47" s="11" t="s">
+    </row>
+    <row r="47" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -4113,14 +3783,9 @@
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
-      <c r="O47" s="6"/>
-      <c r="P47" s="6"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="6"/>
-      <c r="S47" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="15.75">
-      <c r="A48" s="11" t="s">
+    </row>
+    <row r="48" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -4140,21 +3805,16 @@
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
-      <c r="O48" s="6"/>
-      <c r="P48" s="6"/>
-      <c r="Q48" s="6"/>
-      <c r="R48" s="6"/>
-      <c r="S48" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="15.75">
-      <c r="A49" s="11" t="s">
+    </row>
+    <row r="49" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -4167,21 +3827,16 @@
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
-      <c r="O49" s="6"/>
-      <c r="P49" s="6"/>
-      <c r="Q49" s="6"/>
-      <c r="R49" s="6"/>
-      <c r="S49" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="15.75">
-      <c r="A50" s="11" t="s">
+    </row>
+    <row r="50" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -4194,21 +3849,16 @@
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="6"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="6"/>
-      <c r="S50" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="15.75">
-      <c r="A51" s="11" t="s">
+    </row>
+    <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -4221,21 +3871,16 @@
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="6"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="6"/>
-      <c r="S51" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="15.75">
-      <c r="A52" s="11" t="s">
+    </row>
+    <row r="52" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -4248,21 +3893,16 @@
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
-      <c r="O52" s="6"/>
-      <c r="P52" s="6"/>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="6"/>
-      <c r="S52" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="15.75">
-      <c r="A53" s="11" t="s">
+    </row>
+    <row r="53" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -4275,13 +3915,8 @@
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
-      <c r="O53" s="6"/>
-      <c r="P53" s="6"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="6"/>
-      <c r="S53" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="15.75">
+    </row>
+    <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>3</v>
       </c>
@@ -4289,7 +3924,7 @@
         <v>5</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -4302,13 +3937,8 @@
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
-      <c r="O54" s="6"/>
-      <c r="P54" s="6"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="15.75">
+    </row>
+    <row r="55" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>3</v>
       </c>
@@ -4316,7 +3946,7 @@
         <v>5</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -4329,13 +3959,8 @@
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="6"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="6"/>
-      <c r="S55" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="15.75">
+    </row>
+    <row r="56" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>3</v>
       </c>
@@ -4343,7 +3968,7 @@
         <v>5</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -4356,13 +3981,8 @@
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
-      <c r="O56" s="6"/>
-      <c r="P56" s="6"/>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
-      <c r="S56" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="15.75">
+    </row>
+    <row r="57" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>2</v>
       </c>
@@ -4370,7 +3990,7 @@
         <v>5</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -4383,21 +4003,16 @@
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
-      <c r="O57" s="6"/>
-      <c r="P57" s="6"/>
-      <c r="Q57" s="6"/>
-      <c r="R57" s="6"/>
-      <c r="S57" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
-      <c r="A58" s="11" t="s">
+    </row>
+    <row r="58" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -4410,21 +4025,16 @@
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
-      <c r="O58" s="6"/>
-      <c r="P58" s="6"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="6"/>
-      <c r="S58" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
-      <c r="A59" s="11" t="s">
+    </row>
+    <row r="59" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -4437,13 +4047,8 @@
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
-      <c r="O59" s="6"/>
-      <c r="P59" s="6"/>
-      <c r="Q59" s="6"/>
-      <c r="R59" s="6"/>
-      <c r="S59" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
+    </row>
+    <row r="60" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>2</v>
       </c>
@@ -4451,7 +4056,7 @@
         <v>5</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -4464,21 +4069,16 @@
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
-      <c r="O60" s="6"/>
-      <c r="P60" s="6"/>
-      <c r="Q60" s="6"/>
-      <c r="R60" s="6"/>
-      <c r="S60" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
-      <c r="A61" s="11" t="s">
+    </row>
+    <row r="61" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -4491,21 +4091,16 @@
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
-      <c r="O61" s="6"/>
-      <c r="P61" s="6"/>
-      <c r="Q61" s="6"/>
-      <c r="R61" s="6"/>
-      <c r="S61" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
-      <c r="A62" s="11" t="s">
+    </row>
+    <row r="62" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -4518,21 +4113,16 @@
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="6"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
-      <c r="A63" s="11" t="s">
+    </row>
+    <row r="63" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -4545,13 +4135,8 @@
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
-      <c r="O63" s="6"/>
-      <c r="P63" s="6"/>
-      <c r="Q63" s="6"/>
-      <c r="R63" s="6"/>
-      <c r="S63" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
+    </row>
+    <row r="64" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>3</v>
       </c>
@@ -4559,7 +4144,7 @@
         <v>5</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -4572,13 +4157,8 @@
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
-      <c r="O64" s="6"/>
-      <c r="P64" s="6"/>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
+    </row>
+    <row r="65" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>3</v>
       </c>
@@ -4586,7 +4166,7 @@
         <v>5</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -4599,14 +4179,9 @@
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
-      <c r="O65" s="6"/>
-      <c r="P65" s="6"/>
-      <c r="Q65" s="6"/>
-      <c r="R65" s="6"/>
-      <c r="S65" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
-      <c r="A66" s="11" t="s">
+    </row>
+    <row r="66" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -4626,13 +4201,8 @@
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
-      <c r="O66" s="6"/>
-      <c r="P66" s="6"/>
-      <c r="Q66" s="6"/>
-      <c r="R66" s="6"/>
-      <c r="S66" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
+    </row>
+    <row r="67" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>3</v>
       </c>
@@ -4640,7 +4210,7 @@
         <v>6</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -4653,13 +4223,8 @@
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
-      <c r="O67" s="6"/>
-      <c r="P67" s="6"/>
-      <c r="Q67" s="6"/>
-      <c r="R67" s="6"/>
-      <c r="S67" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
+    </row>
+    <row r="68" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>3</v>
       </c>
@@ -4667,7 +4232,7 @@
         <v>6</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -4680,13 +4245,8 @@
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
       <c r="N68" s="1"/>
-      <c r="O68" s="6"/>
-      <c r="P68" s="6"/>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
+    </row>
+    <row r="69" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>2</v>
       </c>
@@ -4694,7 +4254,7 @@
         <v>6</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -4707,13 +4267,8 @@
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
-      <c r="O69" s="6"/>
-      <c r="P69" s="6"/>
-      <c r="Q69" s="6"/>
-      <c r="R69" s="6"/>
-      <c r="S69" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
+    </row>
+    <row r="70" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>2</v>
       </c>
@@ -4721,7 +4276,7 @@
         <v>6</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -4734,13 +4289,8 @@
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
       <c r="N70" s="1"/>
-      <c r="O70" s="6"/>
-      <c r="P70" s="6"/>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="6"/>
-      <c r="S70" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25">
+    </row>
+    <row r="71" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>2</v>
       </c>
@@ -4748,7 +4298,7 @@
         <v>6</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -4761,13 +4311,8 @@
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="6"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="6"/>
-      <c r="S71" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25">
+    </row>
+    <row r="72" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>2</v>
       </c>
@@ -4775,7 +4320,7 @@
         <v>6</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -4788,13 +4333,8 @@
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
       <c r="N72" s="1"/>
-      <c r="O72" s="6"/>
-      <c r="P72" s="6"/>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="17.25">
+    </row>
+    <row r="73" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>2</v>
       </c>
@@ -4802,7 +4342,7 @@
         <v>6</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -4815,13 +4355,8 @@
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
-      <c r="O73" s="6"/>
-      <c r="P73" s="6"/>
-      <c r="Q73" s="6"/>
-      <c r="R73" s="6"/>
-      <c r="S73" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="17.25">
+    </row>
+    <row r="74" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>2</v>
       </c>
@@ -4829,7 +4364,7 @@
         <v>6</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -4842,13 +4377,8 @@
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
-      <c r="O74" s="6"/>
-      <c r="P74" s="6"/>
-      <c r="Q74" s="6"/>
-      <c r="R74" s="6"/>
-      <c r="S74" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25">
+    </row>
+    <row r="75" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>3</v>
       </c>
@@ -4856,7 +4386,7 @@
         <v>6</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -4869,13 +4399,8 @@
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="6"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="6"/>
-      <c r="S75" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
+    </row>
+    <row r="76" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>2</v>
       </c>
@@ -4883,7 +4408,7 @@
         <v>6</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
@@ -4896,13 +4421,8 @@
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="6"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
-      <c r="S76" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25">
+    </row>
+    <row r="77" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>3</v>
       </c>
@@ -4910,7 +4430,7 @@
         <v>6</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -4923,13 +4443,8 @@
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
-      <c r="O77" s="6"/>
-      <c r="P77" s="6"/>
-      <c r="Q77" s="6"/>
-      <c r="R77" s="6"/>
-      <c r="S77" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
+    </row>
+    <row r="78" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>3</v>
       </c>
@@ -4937,7 +4452,7 @@
         <v>6</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -4950,14 +4465,9 @@
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
-      <c r="O78" s="6"/>
-      <c r="P78" s="6"/>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="6"/>
-      <c r="S78" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
-      <c r="A79" s="11" t="s">
+    </row>
+    <row r="79" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -4977,21 +4487,16 @@
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
       <c r="N79" s="1"/>
-      <c r="O79" s="6"/>
-      <c r="P79" s="6"/>
-      <c r="Q79" s="6"/>
-      <c r="R79" s="6"/>
-      <c r="S79" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
-      <c r="A80" s="11" t="s">
+    </row>
+    <row r="80" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -5004,21 +4509,16 @@
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
-      <c r="O80" s="6"/>
-      <c r="P80" s="6"/>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
-      <c r="S80" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
-      <c r="A81" s="11" t="s">
+    </row>
+    <row r="81" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -5031,13 +4531,8 @@
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
-      <c r="O81" s="6"/>
-      <c r="P81" s="6"/>
-      <c r="Q81" s="6"/>
-      <c r="R81" s="6"/>
-      <c r="S81" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25">
+    </row>
+    <row r="82" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>2</v>
       </c>
@@ -5058,13 +4553,8 @@
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
-      <c r="O82" s="6"/>
-      <c r="P82" s="6"/>
-      <c r="Q82" s="6"/>
-      <c r="R82" s="6"/>
-      <c r="S82" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25">
+    </row>
+    <row r="83" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
         <v>2</v>
       </c>
@@ -5072,7 +4562,7 @@
         <v>6</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -5085,13 +4575,8 @@
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
-      <c r="O83" s="6"/>
-      <c r="P83" s="6"/>
-      <c r="Q83" s="6"/>
-      <c r="R83" s="6"/>
-      <c r="S83" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25">
+    </row>
+    <row r="84" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>2</v>
       </c>
@@ -5099,7 +4584,7 @@
         <v>6</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -5112,21 +4597,16 @@
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
       <c r="N84" s="1"/>
-      <c r="O84" s="6"/>
-      <c r="P84" s="6"/>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="6"/>
-      <c r="S84" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25">
-      <c r="A85" s="11" t="s">
+    </row>
+    <row r="85" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -5139,13 +4619,8 @@
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
-      <c r="O85" s="6"/>
-      <c r="P85" s="6"/>
-      <c r="Q85" s="6"/>
-      <c r="R85" s="6"/>
-      <c r="S85" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
+    </row>
+    <row r="86" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
         <v>2</v>
       </c>
@@ -5166,13 +4641,8 @@
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
-      <c r="O86" s="6"/>
-      <c r="P86" s="6"/>
-      <c r="Q86" s="6"/>
-      <c r="R86" s="6"/>
-      <c r="S86" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25">
+    </row>
+    <row r="87" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>3</v>
       </c>
@@ -5180,7 +4650,7 @@
         <v>6</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
@@ -5193,13 +4663,8 @@
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
-      <c r="O87" s="6"/>
-      <c r="P87" s="6"/>
-      <c r="Q87" s="6"/>
-      <c r="R87" s="6"/>
-      <c r="S87" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25">
+    </row>
+    <row r="88" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>2</v>
       </c>
@@ -5207,7 +4672,7 @@
         <v>477</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
@@ -5220,13 +4685,8 @@
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
-      <c r="O88" s="6"/>
-      <c r="P88" s="6"/>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6"/>
-      <c r="S88" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
+    </row>
+    <row r="89" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>2</v>
       </c>
@@ -5234,7 +4694,7 @@
         <v>477</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
@@ -5247,13 +4707,8 @@
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
-      <c r="O89" s="6"/>
-      <c r="P89" s="6"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="6"/>
-      <c r="S89" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25">
+    </row>
+    <row r="90" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>2</v>
       </c>
@@ -5261,7 +4716,7 @@
         <v>477</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
@@ -5274,13 +4729,8 @@
       <c r="L90" s="1"/>
       <c r="M90" s="1"/>
       <c r="N90" s="1"/>
-      <c r="O90" s="6"/>
-      <c r="P90" s="6"/>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="6"/>
-      <c r="S90" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25">
+    </row>
+    <row r="91" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>2</v>
       </c>
@@ -5288,7 +4738,7 @@
         <v>477</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
@@ -5301,37 +4751,9 @@
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
-      <c r="O91" s="6"/>
-      <c r="P91" s="6"/>
-      <c r="Q91" s="6"/>
-      <c r="R91" s="6"/>
-      <c r="S91" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6"/>
-      <c r="L92" s="6"/>
-      <c r="M92" s="6"/>
-      <c r="N92" s="6"/>
-      <c r="O92" s="6"/>
-      <c r="P92" s="6"/>
-      <c r="Q92" s="6"/>
-      <c r="R92" s="6"/>
-      <c r="S92" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
+    </row>
+    <row r="92" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
@@ -5343,79 +4765,11 @@
       <c r="L93" s="1"/>
       <c r="M93" s="1"/>
       <c r="N93" s="1"/>
-      <c r="O93" s="6"/>
-      <c r="P93" s="6"/>
-      <c r="Q93" s="6"/>
-      <c r="R93" s="6"/>
-      <c r="S93" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
-      <c r="M94" s="6"/>
-      <c r="N94" s="6"/>
-      <c r="O94" s="6"/>
-      <c r="P94" s="6"/>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="6"/>
-      <c r="L95" s="6"/>
-      <c r="M95" s="6"/>
-      <c r="N95" s="6"/>
-      <c r="O95" s="6"/>
-      <c r="P95" s="6"/>
-      <c r="Q95" s="6"/>
-      <c r="R95" s="6"/>
-      <c r="S95" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="17.25">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
-      <c r="L96" s="6"/>
-      <c r="M96" s="6"/>
-      <c r="N96" s="6"/>
-      <c r="O96" s="6"/>
-      <c r="P96" s="6"/>
-      <c r="Q96" s="6"/>
-      <c r="R96" s="6"/>
-      <c r="S96" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="17.25">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
+    </row>
+    <row r="94" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" spans="4:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
@@ -5427,16 +4781,8 @@
       <c r="L97" s="1"/>
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
-      <c r="O97" s="6"/>
-      <c r="P97" s="6"/>
-      <c r="Q97" s="6"/>
-      <c r="R97" s="6"/>
-      <c r="S97" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="17.25">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
+    </row>
+    <row r="98" spans="4:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
@@ -5448,16 +4794,8 @@
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
       <c r="N98" s="1"/>
-      <c r="O98" s="6"/>
-      <c r="P98" s="6"/>
-      <c r="Q98" s="6"/>
-      <c r="R98" s="6"/>
-      <c r="S98" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="17.25">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
+    </row>
+    <row r="99" spans="4:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
@@ -5469,16 +4807,8 @@
       <c r="L99" s="1"/>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
-      <c r="O99" s="6"/>
-      <c r="P99" s="6"/>
-      <c r="Q99" s="6"/>
-      <c r="R99" s="6"/>
-      <c r="S99" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="17.25">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
+    </row>
+    <row r="100" spans="4:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
@@ -5490,16 +4820,8 @@
       <c r="L100" s="1"/>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
-      <c r="O100" s="6"/>
-      <c r="P100" s="6"/>
-      <c r="Q100" s="6"/>
-      <c r="R100" s="6"/>
-      <c r="S100" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="17.25">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
+    </row>
+    <row r="101" spans="4:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
@@ -5511,11 +4833,6 @@
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
-      <c r="O101" s="6"/>
-      <c r="P101" s="6"/>
-      <c r="Q101" s="6"/>
-      <c r="R101" s="6"/>
-      <c r="S101" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5523,20 +4840,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5"/>
       <c r="B1" s="5" t="s">
         <v>475</v>
@@ -5548,7 +4864,7 @@
         <v>476</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -5562,7 +4878,7 @@
         <v>479</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -5576,7 +4892,7 @@
         <v>480</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -5590,7 +4906,7 @@
         <v>482</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -5602,7 +4918,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -5614,7 +4930,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -5626,7 +4942,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
@@ -5638,7 +4954,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -5650,7 +4966,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>
@@ -5662,7 +4978,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>2</v>
       </c>
@@ -5674,7 +4990,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
@@ -5686,7 +5002,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>2</v>
       </c>
@@ -5698,7 +5014,7 @@
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>2</v>
       </c>
@@ -5710,7 +5026,7 @@
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>2</v>
       </c>
@@ -5722,7 +5038,7 @@
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>2</v>
       </c>
@@ -5734,7 +5050,7 @@
       </c>
       <c r="D16" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
@@ -5746,7 +5062,7 @@
       </c>
       <c r="D17" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>2</v>
       </c>
@@ -5758,7 +5074,7 @@
       </c>
       <c r="D18" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>2</v>
       </c>
@@ -5770,7 +5086,7 @@
       </c>
       <c r="D19" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>2</v>
       </c>
@@ -5782,7 +5098,7 @@
       </c>
       <c r="D20" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>2</v>
       </c>
@@ -5794,7 +5110,7 @@
       </c>
       <c r="D21" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>2</v>
       </c>
@@ -5806,7 +5122,7 @@
       </c>
       <c r="D22" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>2</v>
       </c>
@@ -5818,8 +5134,8 @@
       </c>
       <c r="D23" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18">
-      <c r="A24" s="11" t="s">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -5830,7 +5146,7 @@
       </c>
       <c r="D24" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>3</v>
       </c>
@@ -5842,8 +5158,8 @@
       </c>
       <c r="D25" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="15.75">
-      <c r="A26" s="11" t="s">
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -5854,8 +5170,8 @@
       </c>
       <c r="D26" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="15.75">
-      <c r="A27" s="11" t="s">
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -5866,7 +5182,7 @@
       </c>
       <c r="D27" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="15.75">
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>2</v>
       </c>
@@ -5878,7 +5194,7 @@
       </c>
       <c r="D28" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="15.75">
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>2</v>
       </c>
@@ -5890,7 +5206,7 @@
       </c>
       <c r="D29" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="15.75">
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>2</v>
       </c>
@@ -5902,7 +5218,7 @@
       </c>
       <c r="D30" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="15.75">
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>2</v>
       </c>
@@ -5914,8 +5230,8 @@
       </c>
       <c r="D31" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="15.75">
-      <c r="A32" s="11" t="s">
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
         <v>338</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -5926,7 +5242,7 @@
       </c>
       <c r="D32" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="15.75">
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>2</v>
       </c>
@@ -5938,7 +5254,7 @@
       </c>
       <c r="D33" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="15.75">
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>2</v>
       </c>
@@ -5950,7 +5266,7 @@
       </c>
       <c r="D34" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="15.75">
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>2</v>
       </c>
@@ -5962,7 +5278,7 @@
       </c>
       <c r="D35" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="15.75">
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>2</v>
       </c>
@@ -5974,7 +5290,7 @@
       </c>
       <c r="D36" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="15.75">
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>2</v>
       </c>
@@ -5986,7 +5302,7 @@
       </c>
       <c r="D37" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="15.75">
+    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>3</v>
       </c>
@@ -5998,7 +5314,7 @@
       </c>
       <c r="D38" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="15.75">
+    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>2</v>
       </c>
@@ -6010,7 +5326,7 @@
       </c>
       <c r="D39" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="15.75">
+    <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>2</v>
       </c>
@@ -6022,7 +5338,7 @@
       </c>
       <c r="D40" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="15.75">
+    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>2</v>
       </c>
@@ -6034,7 +5350,7 @@
       </c>
       <c r="D41" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="15.75">
+    <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>2</v>
       </c>
@@ -6046,7 +5362,7 @@
       </c>
       <c r="D42" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="15.75">
+    <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>2</v>
       </c>
@@ -6058,7 +5374,7 @@
       </c>
       <c r="D43" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="15.75">
+    <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>2</v>
       </c>
@@ -6066,11 +5382,11 @@
         <v>7</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>519</v>
+        <v>674</v>
       </c>
       <c r="D44" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="15.75">
+    <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>2</v>
       </c>
@@ -6078,11 +5394,11 @@
         <v>7</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D45" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="15.75">
+    <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>2</v>
       </c>
@@ -6090,11 +5406,11 @@
         <v>7</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D46" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="15.75">
+    <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>2</v>
       </c>
@@ -6102,11 +5418,11 @@
         <v>7</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D47" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="15.75">
+    <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>2</v>
       </c>
@@ -6114,11 +5430,11 @@
         <v>7</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D48" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="15.75">
+    <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>2</v>
       </c>
@@ -6126,11 +5442,11 @@
         <v>7</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D49" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="15.75">
+    <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>2</v>
       </c>
@@ -6138,11 +5454,11 @@
         <v>7</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D50" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="15.75">
+    <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>2</v>
       </c>
@@ -6150,11 +5466,11 @@
         <v>7</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D51" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="15.75">
+    <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>2</v>
       </c>
@@ -6162,11 +5478,11 @@
         <v>7</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D52" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="15.75">
+    <row r="53" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>2</v>
       </c>
@@ -6174,11 +5490,11 @@
         <v>7</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D53" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="15.75">
+    <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>2</v>
       </c>
@@ -6186,11 +5502,11 @@
         <v>7</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D54" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="15.75">
+    <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>2</v>
       </c>
@@ -6198,11 +5514,11 @@
         <v>7</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D55" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="15.75">
+    <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>2</v>
       </c>
@@ -6210,11 +5526,11 @@
         <v>7</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D56" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="15.75">
+    <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>2</v>
       </c>
@@ -6222,11 +5538,11 @@
         <v>7</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D57" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
+    <row r="58" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>2</v>
       </c>
@@ -6234,11 +5550,11 @@
         <v>7</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D58" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
+    <row r="59" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>2</v>
       </c>
@@ -6246,11 +5562,11 @@
         <v>7</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D59" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
+    <row r="60" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>2</v>
       </c>
@@ -6258,11 +5574,11 @@
         <v>7</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D60" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
+    <row r="61" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>2</v>
       </c>
@@ -6270,11 +5586,11 @@
         <v>7</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D61" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
+    <row r="62" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>3</v>
       </c>
@@ -6282,11 +5598,11 @@
         <v>7</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D62" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
+    <row r="63" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>3</v>
       </c>
@@ -6294,11 +5610,11 @@
         <v>7</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D63" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
+    <row r="64" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>3</v>
       </c>
@@ -6306,11 +5622,11 @@
         <v>7</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D64" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
+    <row r="65" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>3</v>
       </c>
@@ -6318,11 +5634,11 @@
         <v>7</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D65" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
+    <row r="66" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>2</v>
       </c>
@@ -6330,11 +5646,11 @@
         <v>7</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D66" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
+    <row r="67" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>2</v>
       </c>
@@ -6342,11 +5658,11 @@
         <v>7</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D67" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
+    <row r="68" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>2</v>
       </c>
@@ -6354,11 +5670,11 @@
         <v>7</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D68" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
+    <row r="69" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>2</v>
       </c>
@@ -6366,7 +5682,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D69" s="1"/>
     </row>
@@ -6376,182 +5692,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:FJ14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="36" max="36" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="37" max="37" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="39" max="39" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="40" max="40" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="41" max="41" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="42" max="42" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="43" max="43" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="44" max="44" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="45" max="45" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="46" max="46" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="47" max="47" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="48" max="48" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="49" max="49" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="50" max="50" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="51" max="51" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="52" max="52" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="53" max="53" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="54" max="54" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="55" max="55" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="56" max="56" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="57" max="57" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="58" max="58" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="59" max="59" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="60" max="60" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="61" max="61" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="62" max="62" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="63" max="63" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="64" max="64" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="65" max="65" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="66" max="66" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="67" max="67" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="68" max="68" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="69" max="69" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="70" max="70" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="71" max="71" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="72" max="72" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="73" max="73" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="74" max="74" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="75" max="75" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="76" max="76" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="77" max="77" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="78" max="78" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="79" max="79" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="80" max="80" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="81" max="81" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="82" max="82" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="83" max="83" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="84" max="84" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="85" max="85" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="86" max="86" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="87" max="87" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="88" max="88" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="89" max="89" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="90" max="90" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="91" max="91" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="92" max="92" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="93" max="93" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="94" max="94" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="95" max="95" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="96" max="96" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="97" max="97" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="98" max="98" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="99" max="99" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="100" max="100" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="101" max="101" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="102" max="102" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="103" max="103" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="104" max="104" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="105" max="105" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="106" max="106" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="107" max="107" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="108" max="108" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="109" max="109" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="110" max="110" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="111" max="111" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="112" max="112" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="113" max="113" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="114" max="114" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="115" max="115" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="116" max="116" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="117" max="117" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="118" max="118" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="119" max="119" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="120" max="120" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="121" max="121" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="122" max="122" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="123" max="123" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="124" max="124" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="125" max="125" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="126" max="126" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="127" max="127" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="128" max="128" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="129" max="129" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="130" max="130" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="131" max="131" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="132" max="132" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="133" max="133" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="134" max="134" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="135" max="135" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="136" max="136" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="137" max="137" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="138" max="138" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="139" max="139" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="140" max="140" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="141" max="141" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="142" max="142" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="143" max="143" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="144" max="144" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="145" max="145" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="146" max="146" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="147" max="147" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="148" max="148" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="149" max="149" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="150" max="150" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="151" max="151" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="152" max="152" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="153" max="153" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="154" max="154" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="155" max="155" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="156" max="156" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="157" max="157" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="158" max="158" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="159" max="159" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="160" max="160" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="161" max="161" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="162" max="162" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="163" max="163" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="164" max="164" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="165" max="165" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="166" max="166" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="166" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="15.75">
+    <row r="1" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6630,19 +5781,19 @@
       <c r="Z1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="AA1" s="11" t="s">
+      <c r="AA1" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AB1" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AC1" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AD1" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AE1" s="9" t="s">
         <v>338</v>
       </c>
       <c r="AF1" s="4" t="s">
@@ -6672,10 +5823,10 @@
       <c r="AN1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="AO1" s="11" t="s">
+      <c r="AO1" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="AP1" s="11" t="s">
+      <c r="AP1" s="9" t="s">
         <v>338</v>
       </c>
       <c r="AQ1" s="3" t="s">
@@ -6684,22 +5835,22 @@
       <c r="AR1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="AS1" s="11" t="s">
+      <c r="AS1" s="9" t="s">
         <v>338</v>
       </c>
       <c r="AT1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="AU1" s="11" t="s">
+      <c r="AU1" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="AV1" s="11" t="s">
+      <c r="AV1" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="AW1" s="11" t="s">
+      <c r="AW1" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="AX1" s="11" t="s">
+      <c r="AX1" s="9" t="s">
         <v>338</v>
       </c>
       <c r="AY1" s="3" t="s">
@@ -6717,10 +5868,10 @@
       <c r="BC1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="BD1" s="11" t="s">
+      <c r="BD1" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="BE1" s="11" t="s">
+      <c r="BE1" s="9" t="s">
         <v>338</v>
       </c>
       <c r="BF1" s="3" t="s">
@@ -6729,10 +5880,10 @@
       <c r="BG1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="BH1" s="11" t="s">
+      <c r="BH1" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="BI1" s="11" t="s">
+      <c r="BI1" s="9" t="s">
         <v>338</v>
       </c>
       <c r="BJ1" s="3" t="s">
@@ -7051,7 +6202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="15.75">
+    <row r="2" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -7551,7 +6702,7 @@
         <v>344</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="15.75">
+    <row r="3" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
@@ -8051,7 +7202,7 @@
         <v>473</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="15.75">
+    <row r="4" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -8122,7 +7273,7 @@
       <c r="BP4" s="1"/>
       <c r="BQ4" s="1"/>
       <c r="BR4" s="1"/>
-      <c r="BS4" s="12" t="s">
+      <c r="BS4" s="10" t="s">
         <v>474</v>
       </c>
       <c r="BT4" s="1"/>
@@ -8221,1685 +7372,485 @@
       <c r="FI4" s="1"/>
       <c r="FJ4" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="15.75">
-      <c r="A5" s="6"/>
+    <row r="5" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
       <c r="X5" s="1"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
       <c r="AB5" s="1"/>
-      <c r="AC5" s="6"/>
       <c r="AD5" s="1"/>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="6"/>
-      <c r="AG5" s="6"/>
-      <c r="AH5" s="6"/>
-      <c r="AI5" s="6"/>
       <c r="AJ5" s="1"/>
-      <c r="AK5" s="6"/>
-      <c r="AL5" s="6"/>
       <c r="AM5" s="1"/>
-      <c r="AN5" s="6"/>
-      <c r="AO5" s="6"/>
-      <c r="AP5" s="6"/>
-      <c r="AQ5" s="6"/>
-      <c r="AR5" s="6"/>
       <c r="AS5" s="1"/>
-      <c r="AT5" s="6"/>
       <c r="AU5" s="1"/>
-      <c r="AV5" s="6"/>
-      <c r="AW5" s="6"/>
-      <c r="AX5" s="6"/>
-      <c r="AY5" s="6"/>
       <c r="AZ5" s="1"/>
-      <c r="BA5" s="6"/>
-      <c r="BB5" s="6"/>
-      <c r="BC5" s="6"/>
-      <c r="BD5" s="6"/>
       <c r="BE5" s="1"/>
       <c r="BF5" s="1"/>
       <c r="BG5" s="1"/>
-      <c r="BH5" s="6"/>
-      <c r="BI5" s="6"/>
-      <c r="BJ5" s="6"/>
       <c r="BK5" s="1"/>
-      <c r="BL5" s="6"/>
-      <c r="BM5" s="6"/>
       <c r="BN5" s="1"/>
-      <c r="BO5" s="6"/>
-      <c r="BP5" s="6"/>
-      <c r="BQ5" s="6"/>
-      <c r="BR5" s="6"/>
-      <c r="BS5" s="6"/>
-      <c r="BT5" s="6"/>
-      <c r="BU5" s="6"/>
-      <c r="BV5" s="6"/>
-      <c r="BW5" s="6"/>
-      <c r="BX5" s="6"/>
-      <c r="BY5" s="6"/>
-      <c r="BZ5" s="6"/>
-      <c r="CA5" s="6"/>
-      <c r="CB5" s="6"/>
-      <c r="CC5" s="6"/>
-      <c r="CD5" s="6"/>
-      <c r="CE5" s="6"/>
-      <c r="CF5" s="6"/>
-      <c r="CG5" s="6"/>
-      <c r="CH5" s="6"/>
-      <c r="CI5" s="6"/>
-      <c r="CJ5" s="6"/>
-      <c r="CK5" s="6"/>
-      <c r="CL5" s="6"/>
       <c r="CM5" s="1"/>
-      <c r="CN5" s="6"/>
       <c r="CO5" s="1"/>
-      <c r="CP5" s="6"/>
       <c r="CQ5" s="1"/>
-      <c r="CR5" s="6"/>
       <c r="CS5" s="1"/>
-      <c r="CT5" s="6"/>
       <c r="CU5" s="1"/>
-      <c r="CV5" s="6"/>
       <c r="CW5" s="1"/>
-      <c r="CX5" s="6"/>
       <c r="CY5" s="1"/>
-      <c r="CZ5" s="6"/>
       <c r="DA5" s="1"/>
-      <c r="DB5" s="6"/>
       <c r="DC5" s="1"/>
-      <c r="DD5" s="6"/>
       <c r="DE5" s="1"/>
-      <c r="DF5" s="6"/>
-      <c r="DG5" s="6"/>
       <c r="DH5" s="1"/>
-      <c r="DI5" s="6"/>
-      <c r="DJ5" s="6"/>
       <c r="DK5" s="1"/>
-      <c r="DL5" s="6"/>
       <c r="DM5" s="1"/>
-      <c r="DN5" s="6"/>
       <c r="DO5" s="1"/>
-      <c r="DP5" s="6"/>
       <c r="DQ5" s="1"/>
-      <c r="DR5" s="6"/>
       <c r="DS5" s="1"/>
-      <c r="DT5" s="6"/>
       <c r="DU5" s="1"/>
-      <c r="DV5" s="6"/>
       <c r="DW5" s="1"/>
-      <c r="DX5" s="6"/>
       <c r="DY5" s="1"/>
-      <c r="DZ5" s="6"/>
       <c r="EA5" s="1"/>
-      <c r="EB5" s="6"/>
       <c r="EC5" s="1"/>
-      <c r="ED5" s="6"/>
       <c r="EE5" s="1"/>
-      <c r="EF5" s="6"/>
-      <c r="EG5" s="6"/>
       <c r="EH5" s="1"/>
-      <c r="EI5" s="6"/>
-      <c r="EJ5" s="6"/>
       <c r="EK5" s="1"/>
-      <c r="EL5" s="6"/>
       <c r="EM5" s="1"/>
-      <c r="EN5" s="6"/>
       <c r="EO5" s="1"/>
-      <c r="EP5" s="6"/>
       <c r="EQ5" s="1"/>
-      <c r="ER5" s="6"/>
       <c r="ES5" s="1"/>
-      <c r="ET5" s="6"/>
       <c r="EU5" s="1"/>
-      <c r="EV5" s="6"/>
-      <c r="EW5" s="6"/>
-      <c r="EX5" s="6"/>
-      <c r="EY5" s="6"/>
-      <c r="EZ5" s="6"/>
-      <c r="FA5" s="6"/>
-      <c r="FB5" s="6"/>
-      <c r="FC5" s="6"/>
-      <c r="FD5" s="6"/>
-      <c r="FE5" s="6"/>
-      <c r="FF5" s="6"/>
-      <c r="FG5" s="6"/>
-      <c r="FH5" s="6"/>
-      <c r="FI5" s="6"/>
-      <c r="FJ5" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="15.75">
-      <c r="A6" s="6"/>
+    </row>
+    <row r="6" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
       <c r="AB6" s="1"/>
-      <c r="AC6" s="6"/>
       <c r="AD6" s="1"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="6"/>
-      <c r="AO6" s="6"/>
-      <c r="AP6" s="6"/>
-      <c r="AQ6" s="6"/>
-      <c r="AR6" s="6"/>
       <c r="AS6" s="1"/>
-      <c r="AT6" s="6"/>
       <c r="AU6" s="1"/>
-      <c r="AV6" s="6"/>
-      <c r="AW6" s="6"/>
-      <c r="AX6" s="6"/>
-      <c r="AY6" s="6"/>
       <c r="AZ6" s="1"/>
-      <c r="BA6" s="6"/>
-      <c r="BB6" s="6"/>
-      <c r="BC6" s="6"/>
-      <c r="BD6" s="6"/>
       <c r="BE6" s="1"/>
       <c r="BF6" s="1"/>
       <c r="BG6" s="1"/>
-      <c r="BH6" s="6"/>
-      <c r="BI6" s="6"/>
-      <c r="BJ6" s="6"/>
       <c r="BK6" s="1"/>
-      <c r="BL6" s="6"/>
-      <c r="BM6" s="6"/>
       <c r="BN6" s="1"/>
-      <c r="BO6" s="6"/>
-      <c r="BP6" s="6"/>
-      <c r="BQ6" s="6"/>
-      <c r="BR6" s="6"/>
-      <c r="BS6" s="6"/>
-      <c r="BT6" s="6"/>
-      <c r="BU6" s="6"/>
-      <c r="BV6" s="6"/>
-      <c r="BW6" s="6"/>
-      <c r="BX6" s="6"/>
-      <c r="BY6" s="6"/>
-      <c r="BZ6" s="6"/>
-      <c r="CA6" s="6"/>
-      <c r="CB6" s="6"/>
-      <c r="CC6" s="6"/>
-      <c r="CD6" s="6"/>
-      <c r="CE6" s="6"/>
-      <c r="CF6" s="6"/>
-      <c r="CG6" s="6"/>
-      <c r="CH6" s="6"/>
-      <c r="CI6" s="6"/>
-      <c r="CJ6" s="6"/>
-      <c r="CK6" s="6"/>
-      <c r="CL6" s="6"/>
       <c r="CM6" s="1"/>
-      <c r="CN6" s="6"/>
       <c r="CO6" s="1"/>
-      <c r="CP6" s="6"/>
       <c r="CQ6" s="1"/>
-      <c r="CR6" s="6"/>
       <c r="CS6" s="1"/>
-      <c r="CT6" s="6"/>
       <c r="CU6" s="1"/>
-      <c r="CV6" s="6"/>
       <c r="CW6" s="1"/>
-      <c r="CX6" s="6"/>
       <c r="CY6" s="1"/>
-      <c r="CZ6" s="6"/>
       <c r="DA6" s="1"/>
-      <c r="DB6" s="6"/>
       <c r="DC6" s="1"/>
-      <c r="DD6" s="6"/>
       <c r="DE6" s="1"/>
-      <c r="DF6" s="6"/>
-      <c r="DG6" s="6"/>
       <c r="DH6" s="1"/>
-      <c r="DI6" s="6"/>
-      <c r="DJ6" s="6"/>
       <c r="DK6" s="1"/>
-      <c r="DL6" s="6"/>
       <c r="DM6" s="1"/>
-      <c r="DN6" s="6"/>
       <c r="DO6" s="1"/>
-      <c r="DP6" s="6"/>
       <c r="DQ6" s="1"/>
-      <c r="DR6" s="6"/>
       <c r="DS6" s="1"/>
-      <c r="DT6" s="6"/>
       <c r="DU6" s="1"/>
-      <c r="DV6" s="6"/>
       <c r="DW6" s="1"/>
-      <c r="DX6" s="6"/>
       <c r="DY6" s="1"/>
-      <c r="DZ6" s="6"/>
       <c r="EA6" s="1"/>
-      <c r="EB6" s="6"/>
       <c r="EC6" s="1"/>
-      <c r="ED6" s="6"/>
       <c r="EE6" s="1"/>
-      <c r="EF6" s="6"/>
-      <c r="EG6" s="6"/>
       <c r="EH6" s="1"/>
-      <c r="EI6" s="6"/>
-      <c r="EJ6" s="6"/>
       <c r="EK6" s="1"/>
-      <c r="EL6" s="6"/>
       <c r="EM6" s="1"/>
-      <c r="EN6" s="6"/>
       <c r="EO6" s="1"/>
-      <c r="EP6" s="6"/>
       <c r="EQ6" s="1"/>
-      <c r="ER6" s="6"/>
       <c r="ES6" s="1"/>
-      <c r="ET6" s="6"/>
       <c r="EU6" s="1"/>
-      <c r="EV6" s="6"/>
-      <c r="EW6" s="6"/>
-      <c r="EX6" s="6"/>
-      <c r="EY6" s="6"/>
-      <c r="EZ6" s="6"/>
-      <c r="FA6" s="6"/>
-      <c r="FB6" s="6"/>
-      <c r="FC6" s="6"/>
-      <c r="FD6" s="6"/>
-      <c r="FE6" s="6"/>
-      <c r="FF6" s="6"/>
-      <c r="FG6" s="6"/>
-      <c r="FH6" s="6"/>
-      <c r="FI6" s="6"/>
-      <c r="FJ6" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="15.75">
-      <c r="A7" s="6"/>
+    </row>
+    <row r="7" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
       <c r="AB7" s="1"/>
-      <c r="AC7" s="6"/>
       <c r="AD7" s="1"/>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="6"/>
-      <c r="AI7" s="6"/>
       <c r="AJ7" s="1"/>
-      <c r="AK7" s="6"/>
-      <c r="AL7" s="6"/>
       <c r="AM7" s="1"/>
-      <c r="AN7" s="6"/>
-      <c r="AO7" s="6"/>
-      <c r="AP7" s="6"/>
-      <c r="AQ7" s="6"/>
-      <c r="AR7" s="6"/>
       <c r="AS7" s="1"/>
-      <c r="AT7" s="6"/>
       <c r="AU7" s="1"/>
-      <c r="AV7" s="6"/>
-      <c r="AW7" s="6"/>
-      <c r="AX7" s="6"/>
-      <c r="AY7" s="6"/>
       <c r="AZ7" s="1"/>
-      <c r="BA7" s="6"/>
-      <c r="BB7" s="6"/>
-      <c r="BC7" s="6"/>
-      <c r="BD7" s="6"/>
       <c r="BE7" s="1"/>
       <c r="BF7" s="1"/>
       <c r="BG7" s="1"/>
-      <c r="BH7" s="6"/>
-      <c r="BI7" s="6"/>
-      <c r="BJ7" s="6"/>
       <c r="BK7" s="1"/>
-      <c r="BL7" s="6"/>
-      <c r="BM7" s="6"/>
       <c r="BN7" s="1"/>
-      <c r="BO7" s="6"/>
-      <c r="BP7" s="6"/>
-      <c r="BQ7" s="6"/>
-      <c r="BR7" s="6"/>
-      <c r="BS7" s="6"/>
-      <c r="BT7" s="6"/>
-      <c r="BU7" s="6"/>
-      <c r="BV7" s="6"/>
-      <c r="BW7" s="6"/>
-      <c r="BX7" s="6"/>
-      <c r="BY7" s="6"/>
-      <c r="BZ7" s="6"/>
-      <c r="CA7" s="6"/>
-      <c r="CB7" s="6"/>
-      <c r="CC7" s="6"/>
-      <c r="CD7" s="6"/>
-      <c r="CE7" s="6"/>
-      <c r="CF7" s="6"/>
-      <c r="CG7" s="6"/>
-      <c r="CH7" s="6"/>
-      <c r="CI7" s="6"/>
-      <c r="CJ7" s="6"/>
-      <c r="CK7" s="6"/>
-      <c r="CL7" s="6"/>
       <c r="CM7" s="1"/>
-      <c r="CN7" s="6"/>
       <c r="CO7" s="1"/>
-      <c r="CP7" s="6"/>
       <c r="CQ7" s="1"/>
-      <c r="CR7" s="6"/>
       <c r="CS7" s="1"/>
-      <c r="CT7" s="6"/>
       <c r="CU7" s="1"/>
-      <c r="CV7" s="6"/>
       <c r="CW7" s="1"/>
-      <c r="CX7" s="6"/>
       <c r="CY7" s="1"/>
-      <c r="CZ7" s="6"/>
       <c r="DA7" s="1"/>
-      <c r="DB7" s="6"/>
       <c r="DC7" s="1"/>
-      <c r="DD7" s="6"/>
       <c r="DE7" s="1"/>
-      <c r="DF7" s="6"/>
-      <c r="DG7" s="6"/>
       <c r="DH7" s="1"/>
-      <c r="DI7" s="6"/>
-      <c r="DJ7" s="6"/>
       <c r="DK7" s="1"/>
-      <c r="DL7" s="6"/>
       <c r="DM7" s="1"/>
-      <c r="DN7" s="6"/>
       <c r="DO7" s="1"/>
-      <c r="DP7" s="6"/>
       <c r="DQ7" s="1"/>
-      <c r="DR7" s="6"/>
       <c r="DS7" s="1"/>
-      <c r="DT7" s="6"/>
       <c r="DU7" s="1"/>
-      <c r="DV7" s="6"/>
       <c r="DW7" s="1"/>
-      <c r="DX7" s="6"/>
       <c r="DY7" s="1"/>
-      <c r="DZ7" s="6"/>
       <c r="EA7" s="1"/>
-      <c r="EB7" s="6"/>
       <c r="EC7" s="1"/>
-      <c r="ED7" s="6"/>
       <c r="EE7" s="1"/>
-      <c r="EF7" s="6"/>
-      <c r="EG7" s="6"/>
       <c r="EH7" s="1"/>
-      <c r="EI7" s="6"/>
-      <c r="EJ7" s="6"/>
       <c r="EK7" s="1"/>
-      <c r="EL7" s="6"/>
       <c r="EM7" s="1"/>
-      <c r="EN7" s="6"/>
       <c r="EO7" s="1"/>
-      <c r="EP7" s="6"/>
       <c r="EQ7" s="1"/>
-      <c r="ER7" s="6"/>
       <c r="ES7" s="1"/>
-      <c r="ET7" s="6"/>
       <c r="EU7" s="1"/>
-      <c r="EV7" s="6"/>
-      <c r="EW7" s="6"/>
-      <c r="EX7" s="6"/>
-      <c r="EY7" s="6"/>
-      <c r="EZ7" s="6"/>
-      <c r="FA7" s="6"/>
-      <c r="FB7" s="6"/>
-      <c r="FC7" s="6"/>
-      <c r="FD7" s="6"/>
-      <c r="FE7" s="6"/>
-      <c r="FF7" s="6"/>
-      <c r="FG7" s="6"/>
-      <c r="FH7" s="6"/>
-      <c r="FI7" s="6"/>
-      <c r="FJ7" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="15.75">
-      <c r="A8" s="6"/>
+    </row>
+    <row r="8" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
       <c r="X8" s="1"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
       <c r="AB8" s="1"/>
-      <c r="AC8" s="6"/>
       <c r="AD8" s="1"/>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-      <c r="AG8" s="6"/>
-      <c r="AH8" s="6"/>
-      <c r="AI8" s="6"/>
       <c r="AJ8" s="1"/>
-      <c r="AK8" s="6"/>
-      <c r="AL8" s="6"/>
       <c r="AM8" s="1"/>
-      <c r="AN8" s="6"/>
-      <c r="AO8" s="6"/>
-      <c r="AP8" s="6"/>
-      <c r="AQ8" s="6"/>
-      <c r="AR8" s="6"/>
       <c r="AS8" s="1"/>
-      <c r="AT8" s="6"/>
       <c r="AU8" s="1"/>
-      <c r="AV8" s="6"/>
-      <c r="AW8" s="6"/>
-      <c r="AX8" s="6"/>
-      <c r="AY8" s="6"/>
       <c r="AZ8" s="1"/>
-      <c r="BA8" s="6"/>
-      <c r="BB8" s="6"/>
-      <c r="BC8" s="6"/>
-      <c r="BD8" s="6"/>
       <c r="BE8" s="1"/>
       <c r="BF8" s="1"/>
       <c r="BG8" s="1"/>
-      <c r="BH8" s="6"/>
-      <c r="BI8" s="6"/>
-      <c r="BJ8" s="6"/>
       <c r="BK8" s="1"/>
-      <c r="BL8" s="6"/>
-      <c r="BM8" s="6"/>
       <c r="BN8" s="1"/>
-      <c r="BO8" s="6"/>
-      <c r="BP8" s="6"/>
-      <c r="BQ8" s="6"/>
-      <c r="BR8" s="6"/>
-      <c r="BS8" s="6"/>
-      <c r="BT8" s="6"/>
-      <c r="BU8" s="6"/>
-      <c r="BV8" s="6"/>
-      <c r="BW8" s="6"/>
-      <c r="BX8" s="6"/>
-      <c r="BY8" s="6"/>
-      <c r="BZ8" s="6"/>
-      <c r="CA8" s="6"/>
-      <c r="CB8" s="6"/>
-      <c r="CC8" s="6"/>
-      <c r="CD8" s="6"/>
-      <c r="CE8" s="6"/>
-      <c r="CF8" s="6"/>
-      <c r="CG8" s="6"/>
-      <c r="CH8" s="6"/>
-      <c r="CI8" s="6"/>
-      <c r="CJ8" s="6"/>
-      <c r="CK8" s="6"/>
-      <c r="CL8" s="6"/>
       <c r="CM8" s="1"/>
-      <c r="CN8" s="6"/>
       <c r="CO8" s="1"/>
-      <c r="CP8" s="6"/>
       <c r="CQ8" s="1"/>
-      <c r="CR8" s="6"/>
       <c r="CS8" s="1"/>
-      <c r="CT8" s="6"/>
       <c r="CU8" s="1"/>
-      <c r="CV8" s="6"/>
       <c r="CW8" s="1"/>
-      <c r="CX8" s="6"/>
       <c r="CY8" s="1"/>
-      <c r="CZ8" s="6"/>
       <c r="DA8" s="1"/>
-      <c r="DB8" s="6"/>
       <c r="DC8" s="1"/>
-      <c r="DD8" s="6"/>
       <c r="DE8" s="1"/>
-      <c r="DF8" s="6"/>
-      <c r="DG8" s="6"/>
       <c r="DH8" s="1"/>
-      <c r="DI8" s="6"/>
-      <c r="DJ8" s="6"/>
       <c r="DK8" s="1"/>
-      <c r="DL8" s="6"/>
       <c r="DM8" s="1"/>
-      <c r="DN8" s="6"/>
       <c r="DO8" s="1"/>
-      <c r="DP8" s="6"/>
       <c r="DQ8" s="1"/>
-      <c r="DR8" s="6"/>
       <c r="DS8" s="1"/>
-      <c r="DT8" s="6"/>
       <c r="DU8" s="1"/>
-      <c r="DV8" s="6"/>
       <c r="DW8" s="1"/>
-      <c r="DX8" s="6"/>
       <c r="DY8" s="1"/>
-      <c r="DZ8" s="6"/>
       <c r="EA8" s="1"/>
-      <c r="EB8" s="6"/>
       <c r="EC8" s="1"/>
-      <c r="ED8" s="6"/>
       <c r="EE8" s="1"/>
-      <c r="EF8" s="6"/>
-      <c r="EG8" s="6"/>
       <c r="EH8" s="1"/>
-      <c r="EI8" s="6"/>
-      <c r="EJ8" s="6"/>
       <c r="EK8" s="1"/>
-      <c r="EL8" s="6"/>
       <c r="EM8" s="1"/>
-      <c r="EN8" s="6"/>
       <c r="EO8" s="1"/>
-      <c r="EP8" s="6"/>
       <c r="EQ8" s="1"/>
-      <c r="ER8" s="6"/>
       <c r="ES8" s="1"/>
-      <c r="ET8" s="6"/>
       <c r="EU8" s="1"/>
-      <c r="EV8" s="6"/>
-      <c r="EW8" s="6"/>
-      <c r="EX8" s="6"/>
-      <c r="EY8" s="6"/>
-      <c r="EZ8" s="6"/>
-      <c r="FA8" s="6"/>
-      <c r="FB8" s="6"/>
-      <c r="FC8" s="6"/>
-      <c r="FD8" s="6"/>
-      <c r="FE8" s="6"/>
-      <c r="FF8" s="6"/>
-      <c r="FG8" s="6"/>
-      <c r="FH8" s="6"/>
-      <c r="FI8" s="6"/>
-      <c r="FJ8" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="15.75">
-      <c r="A9" s="6"/>
+    </row>
+    <row r="9" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
       <c r="X9" s="1"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
       <c r="AB9" s="1"/>
-      <c r="AC9" s="6"/>
       <c r="AD9" s="1"/>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-      <c r="AG9" s="6"/>
-      <c r="AH9" s="6"/>
-      <c r="AI9" s="6"/>
       <c r="AJ9" s="1"/>
-      <c r="AK9" s="6"/>
-      <c r="AL9" s="6"/>
       <c r="AM9" s="1"/>
-      <c r="AN9" s="6"/>
-      <c r="AO9" s="6"/>
-      <c r="AP9" s="6"/>
-      <c r="AQ9" s="6"/>
-      <c r="AR9" s="6"/>
       <c r="AS9" s="1"/>
-      <c r="AT9" s="6"/>
       <c r="AU9" s="1"/>
-      <c r="AV9" s="6"/>
-      <c r="AW9" s="6"/>
-      <c r="AX9" s="6"/>
-      <c r="AY9" s="6"/>
       <c r="AZ9" s="1"/>
-      <c r="BA9" s="6"/>
-      <c r="BB9" s="6"/>
-      <c r="BC9" s="6"/>
-      <c r="BD9" s="6"/>
       <c r="BE9" s="1"/>
       <c r="BF9" s="1"/>
       <c r="BG9" s="1"/>
-      <c r="BH9" s="6"/>
-      <c r="BI9" s="6"/>
-      <c r="BJ9" s="6"/>
       <c r="BK9" s="1"/>
-      <c r="BL9" s="6"/>
-      <c r="BM9" s="6"/>
       <c r="BN9" s="1"/>
-      <c r="BO9" s="6"/>
-      <c r="BP9" s="6"/>
-      <c r="BQ9" s="6"/>
-      <c r="BR9" s="6"/>
-      <c r="BS9" s="6"/>
-      <c r="BT9" s="6"/>
-      <c r="BU9" s="6"/>
-      <c r="BV9" s="6"/>
-      <c r="BW9" s="6"/>
-      <c r="BX9" s="6"/>
-      <c r="BY9" s="6"/>
-      <c r="BZ9" s="6"/>
-      <c r="CA9" s="6"/>
-      <c r="CB9" s="6"/>
-      <c r="CC9" s="6"/>
-      <c r="CD9" s="6"/>
-      <c r="CE9" s="6"/>
-      <c r="CF9" s="6"/>
-      <c r="CG9" s="6"/>
-      <c r="CH9" s="6"/>
-      <c r="CI9" s="6"/>
-      <c r="CJ9" s="6"/>
-      <c r="CK9" s="6"/>
-      <c r="CL9" s="6"/>
       <c r="CM9" s="1"/>
-      <c r="CN9" s="6"/>
       <c r="CO9" s="1"/>
-      <c r="CP9" s="6"/>
       <c r="CQ9" s="1"/>
-      <c r="CR9" s="6"/>
       <c r="CS9" s="1"/>
-      <c r="CT9" s="6"/>
       <c r="CU9" s="1"/>
-      <c r="CV9" s="6"/>
       <c r="CW9" s="1"/>
-      <c r="CX9" s="6"/>
       <c r="CY9" s="1"/>
-      <c r="CZ9" s="6"/>
       <c r="DA9" s="1"/>
-      <c r="DB9" s="6"/>
       <c r="DC9" s="1"/>
-      <c r="DD9" s="6"/>
       <c r="DE9" s="1"/>
-      <c r="DF9" s="6"/>
-      <c r="DG9" s="6"/>
       <c r="DH9" s="1"/>
-      <c r="DI9" s="6"/>
-      <c r="DJ9" s="6"/>
       <c r="DK9" s="1"/>
-      <c r="DL9" s="6"/>
       <c r="DM9" s="1"/>
-      <c r="DN9" s="6"/>
       <c r="DO9" s="1"/>
-      <c r="DP9" s="6"/>
       <c r="DQ9" s="1"/>
-      <c r="DR9" s="6"/>
       <c r="DS9" s="1"/>
-      <c r="DT9" s="6"/>
       <c r="DU9" s="1"/>
-      <c r="DV9" s="6"/>
       <c r="DW9" s="1"/>
-      <c r="DX9" s="6"/>
       <c r="DY9" s="1"/>
-      <c r="DZ9" s="6"/>
       <c r="EA9" s="1"/>
-      <c r="EB9" s="6"/>
       <c r="EC9" s="1"/>
-      <c r="ED9" s="6"/>
       <c r="EE9" s="1"/>
-      <c r="EF9" s="6"/>
-      <c r="EG9" s="6"/>
       <c r="EH9" s="1"/>
-      <c r="EI9" s="6"/>
-      <c r="EJ9" s="6"/>
       <c r="EK9" s="1"/>
-      <c r="EL9" s="6"/>
       <c r="EM9" s="1"/>
-      <c r="EN9" s="6"/>
       <c r="EO9" s="1"/>
-      <c r="EP9" s="6"/>
       <c r="EQ9" s="1"/>
-      <c r="ER9" s="6"/>
       <c r="ES9" s="1"/>
-      <c r="ET9" s="6"/>
       <c r="EU9" s="1"/>
-      <c r="EV9" s="6"/>
-      <c r="EW9" s="6"/>
-      <c r="EX9" s="6"/>
-      <c r="EY9" s="6"/>
-      <c r="EZ9" s="6"/>
-      <c r="FA9" s="6"/>
-      <c r="FB9" s="6"/>
-      <c r="FC9" s="6"/>
-      <c r="FD9" s="6"/>
-      <c r="FE9" s="6"/>
-      <c r="FF9" s="6"/>
-      <c r="FG9" s="6"/>
-      <c r="FH9" s="6"/>
-      <c r="FI9" s="6"/>
-      <c r="FJ9" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="15.75">
-      <c r="A10" s="6"/>
+    </row>
+    <row r="10" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
       <c r="X10" s="1"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="6"/>
       <c r="AB10" s="1"/>
-      <c r="AC10" s="6"/>
       <c r="AD10" s="1"/>
-      <c r="AE10" s="6"/>
-      <c r="AF10" s="6"/>
-      <c r="AG10" s="6"/>
-      <c r="AH10" s="6"/>
-      <c r="AI10" s="6"/>
       <c r="AJ10" s="1"/>
-      <c r="AK10" s="6"/>
-      <c r="AL10" s="6"/>
       <c r="AM10" s="1"/>
-      <c r="AN10" s="6"/>
-      <c r="AO10" s="6"/>
-      <c r="AP10" s="6"/>
-      <c r="AQ10" s="6"/>
-      <c r="AR10" s="6"/>
       <c r="AS10" s="1"/>
-      <c r="AT10" s="6"/>
       <c r="AU10" s="1"/>
-      <c r="AV10" s="6"/>
-      <c r="AW10" s="6"/>
-      <c r="AX10" s="6"/>
-      <c r="AY10" s="6"/>
       <c r="AZ10" s="1"/>
-      <c r="BA10" s="6"/>
-      <c r="BB10" s="6"/>
-      <c r="BC10" s="6"/>
-      <c r="BD10" s="6"/>
       <c r="BE10" s="1"/>
       <c r="BF10" s="1"/>
       <c r="BG10" s="1"/>
-      <c r="BH10" s="6"/>
-      <c r="BI10" s="6"/>
-      <c r="BJ10" s="6"/>
       <c r="BK10" s="1"/>
-      <c r="BL10" s="6"/>
-      <c r="BM10" s="6"/>
       <c r="BN10" s="1"/>
-      <c r="BO10" s="6"/>
-      <c r="BP10" s="6"/>
-      <c r="BQ10" s="6"/>
-      <c r="BR10" s="6"/>
-      <c r="BS10" s="6"/>
-      <c r="BT10" s="6"/>
-      <c r="BU10" s="6"/>
-      <c r="BV10" s="6"/>
-      <c r="BW10" s="6"/>
-      <c r="BX10" s="6"/>
-      <c r="BY10" s="6"/>
-      <c r="BZ10" s="6"/>
-      <c r="CA10" s="6"/>
-      <c r="CB10" s="6"/>
-      <c r="CC10" s="6"/>
-      <c r="CD10" s="6"/>
-      <c r="CE10" s="6"/>
-      <c r="CF10" s="6"/>
-      <c r="CG10" s="6"/>
-      <c r="CH10" s="6"/>
-      <c r="CI10" s="6"/>
-      <c r="CJ10" s="6"/>
-      <c r="CK10" s="6"/>
-      <c r="CL10" s="6"/>
       <c r="CM10" s="1"/>
-      <c r="CN10" s="6"/>
       <c r="CO10" s="1"/>
-      <c r="CP10" s="6"/>
       <c r="CQ10" s="1"/>
-      <c r="CR10" s="6"/>
       <c r="CS10" s="1"/>
-      <c r="CT10" s="6"/>
       <c r="CU10" s="1"/>
-      <c r="CV10" s="6"/>
       <c r="CW10" s="1"/>
-      <c r="CX10" s="6"/>
       <c r="CY10" s="1"/>
-      <c r="CZ10" s="6"/>
       <c r="DA10" s="1"/>
-      <c r="DB10" s="6"/>
       <c r="DC10" s="1"/>
-      <c r="DD10" s="6"/>
       <c r="DE10" s="1"/>
-      <c r="DF10" s="6"/>
-      <c r="DG10" s="6"/>
       <c r="DH10" s="1"/>
-      <c r="DI10" s="6"/>
-      <c r="DJ10" s="6"/>
       <c r="DK10" s="1"/>
-      <c r="DL10" s="6"/>
       <c r="DM10" s="1"/>
-      <c r="DN10" s="6"/>
       <c r="DO10" s="1"/>
-      <c r="DP10" s="6"/>
       <c r="DQ10" s="1"/>
-      <c r="DR10" s="6"/>
       <c r="DS10" s="1"/>
-      <c r="DT10" s="6"/>
       <c r="DU10" s="1"/>
-      <c r="DV10" s="6"/>
       <c r="DW10" s="1"/>
-      <c r="DX10" s="6"/>
       <c r="DY10" s="1"/>
-      <c r="DZ10" s="6"/>
       <c r="EA10" s="1"/>
-      <c r="EB10" s="6"/>
       <c r="EC10" s="1"/>
-      <c r="ED10" s="6"/>
       <c r="EE10" s="1"/>
-      <c r="EF10" s="6"/>
-      <c r="EG10" s="6"/>
       <c r="EH10" s="1"/>
-      <c r="EI10" s="6"/>
-      <c r="EJ10" s="6"/>
       <c r="EK10" s="1"/>
-      <c r="EL10" s="6"/>
       <c r="EM10" s="1"/>
-      <c r="EN10" s="6"/>
       <c r="EO10" s="1"/>
-      <c r="EP10" s="6"/>
       <c r="EQ10" s="1"/>
-      <c r="ER10" s="6"/>
       <c r="ES10" s="1"/>
-      <c r="ET10" s="6"/>
       <c r="EU10" s="1"/>
-      <c r="EV10" s="6"/>
-      <c r="EW10" s="6"/>
-      <c r="EX10" s="6"/>
-      <c r="EY10" s="6"/>
-      <c r="EZ10" s="6"/>
-      <c r="FA10" s="6"/>
-      <c r="FB10" s="6"/>
-      <c r="FC10" s="6"/>
-      <c r="FD10" s="6"/>
-      <c r="FE10" s="6"/>
-      <c r="FF10" s="6"/>
-      <c r="FG10" s="6"/>
-      <c r="FH10" s="6"/>
-      <c r="FI10" s="6"/>
-      <c r="FJ10" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="15.75">
-      <c r="A11" s="6"/>
+    </row>
+    <row r="11" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
       <c r="X11" s="1"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="6"/>
       <c r="AB11" s="1"/>
-      <c r="AC11" s="6"/>
       <c r="AD11" s="1"/>
-      <c r="AE11" s="6"/>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="6"/>
-      <c r="AI11" s="6"/>
       <c r="AJ11" s="1"/>
-      <c r="AK11" s="6"/>
-      <c r="AL11" s="6"/>
       <c r="AM11" s="1"/>
-      <c r="AN11" s="6"/>
-      <c r="AO11" s="6"/>
-      <c r="AP11" s="6"/>
-      <c r="AQ11" s="6"/>
-      <c r="AR11" s="6"/>
       <c r="AS11" s="1"/>
-      <c r="AT11" s="6"/>
       <c r="AU11" s="1"/>
-      <c r="AV11" s="6"/>
-      <c r="AW11" s="6"/>
-      <c r="AX11" s="6"/>
-      <c r="AY11" s="6"/>
       <c r="AZ11" s="1"/>
-      <c r="BA11" s="6"/>
-      <c r="BB11" s="6"/>
-      <c r="BC11" s="6"/>
-      <c r="BD11" s="6"/>
       <c r="BE11" s="1"/>
       <c r="BF11" s="1"/>
       <c r="BG11" s="1"/>
-      <c r="BH11" s="6"/>
-      <c r="BI11" s="6"/>
-      <c r="BJ11" s="6"/>
       <c r="BK11" s="1"/>
-      <c r="BL11" s="6"/>
-      <c r="BM11" s="6"/>
       <c r="BN11" s="1"/>
-      <c r="BO11" s="6"/>
-      <c r="BP11" s="6"/>
-      <c r="BQ11" s="6"/>
-      <c r="BR11" s="6"/>
-      <c r="BS11" s="6"/>
-      <c r="BT11" s="6"/>
-      <c r="BU11" s="6"/>
-      <c r="BV11" s="6"/>
-      <c r="BW11" s="6"/>
-      <c r="BX11" s="6"/>
-      <c r="BY11" s="6"/>
-      <c r="BZ11" s="6"/>
-      <c r="CA11" s="6"/>
-      <c r="CB11" s="6"/>
-      <c r="CC11" s="6"/>
-      <c r="CD11" s="6"/>
-      <c r="CE11" s="6"/>
-      <c r="CF11" s="6"/>
-      <c r="CG11" s="6"/>
-      <c r="CH11" s="6"/>
-      <c r="CI11" s="6"/>
-      <c r="CJ11" s="6"/>
-      <c r="CK11" s="6"/>
-      <c r="CL11" s="6"/>
       <c r="CM11" s="1"/>
-      <c r="CN11" s="6"/>
       <c r="CO11" s="1"/>
-      <c r="CP11" s="6"/>
       <c r="CQ11" s="1"/>
-      <c r="CR11" s="6"/>
       <c r="CS11" s="1"/>
-      <c r="CT11" s="6"/>
       <c r="CU11" s="1"/>
-      <c r="CV11" s="6"/>
       <c r="CW11" s="1"/>
-      <c r="CX11" s="6"/>
       <c r="CY11" s="1"/>
-      <c r="CZ11" s="6"/>
       <c r="DA11" s="1"/>
-      <c r="DB11" s="6"/>
       <c r="DC11" s="1"/>
-      <c r="DD11" s="6"/>
       <c r="DE11" s="1"/>
-      <c r="DF11" s="6"/>
-      <c r="DG11" s="6"/>
       <c r="DH11" s="1"/>
-      <c r="DI11" s="6"/>
-      <c r="DJ11" s="6"/>
       <c r="DK11" s="1"/>
-      <c r="DL11" s="6"/>
       <c r="DM11" s="1"/>
-      <c r="DN11" s="6"/>
       <c r="DO11" s="1"/>
-      <c r="DP11" s="6"/>
       <c r="DQ11" s="1"/>
-      <c r="DR11" s="6"/>
       <c r="DS11" s="1"/>
-      <c r="DT11" s="6"/>
       <c r="DU11" s="1"/>
-      <c r="DV11" s="6"/>
       <c r="DW11" s="1"/>
-      <c r="DX11" s="6"/>
       <c r="DY11" s="1"/>
-      <c r="DZ11" s="6"/>
       <c r="EA11" s="1"/>
-      <c r="EB11" s="6"/>
       <c r="EC11" s="1"/>
-      <c r="ED11" s="6"/>
       <c r="EE11" s="1"/>
-      <c r="EF11" s="6"/>
-      <c r="EG11" s="6"/>
       <c r="EH11" s="1"/>
-      <c r="EI11" s="6"/>
-      <c r="EJ11" s="6"/>
       <c r="EK11" s="1"/>
-      <c r="EL11" s="6"/>
       <c r="EM11" s="1"/>
-      <c r="EN11" s="6"/>
       <c r="EO11" s="1"/>
-      <c r="EP11" s="6"/>
       <c r="EQ11" s="1"/>
-      <c r="ER11" s="6"/>
       <c r="ES11" s="1"/>
-      <c r="ET11" s="6"/>
       <c r="EU11" s="1"/>
-      <c r="EV11" s="6"/>
-      <c r="EW11" s="6"/>
-      <c r="EX11" s="6"/>
-      <c r="EY11" s="6"/>
-      <c r="EZ11" s="6"/>
-      <c r="FA11" s="6"/>
-      <c r="FB11" s="6"/>
-      <c r="FC11" s="6"/>
-      <c r="FD11" s="6"/>
-      <c r="FE11" s="6"/>
-      <c r="FF11" s="6"/>
-      <c r="FG11" s="6"/>
-      <c r="FH11" s="6"/>
-      <c r="FI11" s="6"/>
-      <c r="FJ11" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="15.75">
-      <c r="A12" s="6"/>
+    </row>
+    <row r="12" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
       <c r="X12" s="1"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="6"/>
       <c r="AB12" s="1"/>
-      <c r="AC12" s="6"/>
       <c r="AD12" s="1"/>
-      <c r="AE12" s="6"/>
-      <c r="AF12" s="6"/>
-      <c r="AG12" s="6"/>
-      <c r="AH12" s="6"/>
-      <c r="AI12" s="6"/>
       <c r="AJ12" s="1"/>
-      <c r="AK12" s="6"/>
-      <c r="AL12" s="6"/>
       <c r="AM12" s="1"/>
-      <c r="AN12" s="6"/>
-      <c r="AO12" s="6"/>
-      <c r="AP12" s="6"/>
-      <c r="AQ12" s="6"/>
-      <c r="AR12" s="6"/>
       <c r="AS12" s="1"/>
-      <c r="AT12" s="6"/>
       <c r="AU12" s="1"/>
-      <c r="AV12" s="6"/>
-      <c r="AW12" s="6"/>
-      <c r="AX12" s="6"/>
-      <c r="AY12" s="6"/>
       <c r="AZ12" s="1"/>
-      <c r="BA12" s="6"/>
-      <c r="BB12" s="6"/>
-      <c r="BC12" s="6"/>
-      <c r="BD12" s="6"/>
       <c r="BE12" s="1"/>
       <c r="BF12" s="1"/>
       <c r="BG12" s="1"/>
-      <c r="BH12" s="6"/>
-      <c r="BI12" s="6"/>
-      <c r="BJ12" s="6"/>
       <c r="BK12" s="1"/>
-      <c r="BL12" s="6"/>
-      <c r="BM12" s="6"/>
       <c r="BN12" s="1"/>
-      <c r="BO12" s="6"/>
-      <c r="BP12" s="6"/>
-      <c r="BQ12" s="6"/>
-      <c r="BR12" s="6"/>
-      <c r="BS12" s="6"/>
-      <c r="BT12" s="6"/>
-      <c r="BU12" s="6"/>
-      <c r="BV12" s="6"/>
-      <c r="BW12" s="6"/>
-      <c r="BX12" s="6"/>
-      <c r="BY12" s="6"/>
-      <c r="BZ12" s="6"/>
-      <c r="CA12" s="6"/>
-      <c r="CB12" s="6"/>
-      <c r="CC12" s="6"/>
-      <c r="CD12" s="6"/>
-      <c r="CE12" s="6"/>
-      <c r="CF12" s="6"/>
-      <c r="CG12" s="6"/>
-      <c r="CH12" s="6"/>
-      <c r="CI12" s="6"/>
-      <c r="CJ12" s="6"/>
-      <c r="CK12" s="6"/>
-      <c r="CL12" s="6"/>
       <c r="CM12" s="1"/>
-      <c r="CN12" s="6"/>
       <c r="CO12" s="1"/>
-      <c r="CP12" s="6"/>
       <c r="CQ12" s="1"/>
-      <c r="CR12" s="6"/>
       <c r="CS12" s="1"/>
-      <c r="CT12" s="6"/>
       <c r="CU12" s="1"/>
-      <c r="CV12" s="6"/>
       <c r="CW12" s="1"/>
-      <c r="CX12" s="6"/>
       <c r="CY12" s="1"/>
-      <c r="CZ12" s="6"/>
       <c r="DA12" s="1"/>
-      <c r="DB12" s="6"/>
       <c r="DC12" s="1"/>
-      <c r="DD12" s="6"/>
       <c r="DE12" s="1"/>
-      <c r="DF12" s="6"/>
-      <c r="DG12" s="6"/>
       <c r="DH12" s="1"/>
-      <c r="DI12" s="6"/>
-      <c r="DJ12" s="6"/>
       <c r="DK12" s="1"/>
-      <c r="DL12" s="6"/>
       <c r="DM12" s="1"/>
-      <c r="DN12" s="6"/>
       <c r="DO12" s="1"/>
-      <c r="DP12" s="6"/>
       <c r="DQ12" s="1"/>
-      <c r="DR12" s="6"/>
       <c r="DS12" s="1"/>
-      <c r="DT12" s="6"/>
       <c r="DU12" s="1"/>
-      <c r="DV12" s="6"/>
       <c r="DW12" s="1"/>
-      <c r="DX12" s="6"/>
       <c r="DY12" s="1"/>
-      <c r="DZ12" s="6"/>
       <c r="EA12" s="1"/>
-      <c r="EB12" s="6"/>
       <c r="EC12" s="1"/>
-      <c r="ED12" s="6"/>
       <c r="EE12" s="1"/>
-      <c r="EF12" s="6"/>
-      <c r="EG12" s="6"/>
       <c r="EH12" s="1"/>
-      <c r="EI12" s="6"/>
-      <c r="EJ12" s="6"/>
       <c r="EK12" s="1"/>
-      <c r="EL12" s="6"/>
       <c r="EM12" s="1"/>
-      <c r="EN12" s="6"/>
       <c r="EO12" s="1"/>
-      <c r="EP12" s="6"/>
       <c r="EQ12" s="1"/>
-      <c r="ER12" s="6"/>
       <c r="ES12" s="1"/>
-      <c r="ET12" s="6"/>
       <c r="EU12" s="1"/>
-      <c r="EV12" s="6"/>
-      <c r="EW12" s="6"/>
-      <c r="EX12" s="6"/>
-      <c r="EY12" s="6"/>
-      <c r="EZ12" s="6"/>
-      <c r="FA12" s="6"/>
-      <c r="FB12" s="6"/>
-      <c r="FC12" s="6"/>
-      <c r="FD12" s="6"/>
-      <c r="FE12" s="6"/>
-      <c r="FF12" s="6"/>
-      <c r="FG12" s="6"/>
-      <c r="FH12" s="6"/>
-      <c r="FI12" s="6"/>
-      <c r="FJ12" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="15.75">
-      <c r="A13" s="6"/>
+    </row>
+    <row r="13" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
       <c r="X13" s="1"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="6"/>
       <c r="AB13" s="1"/>
-      <c r="AC13" s="6"/>
       <c r="AD13" s="1"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
       <c r="AJ13" s="1"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
       <c r="AM13" s="1"/>
-      <c r="AN13" s="6"/>
-      <c r="AO13" s="6"/>
-      <c r="AP13" s="6"/>
-      <c r="AQ13" s="6"/>
-      <c r="AR13" s="6"/>
       <c r="AS13" s="1"/>
-      <c r="AT13" s="6"/>
       <c r="AU13" s="1"/>
-      <c r="AV13" s="6"/>
-      <c r="AW13" s="6"/>
-      <c r="AX13" s="6"/>
-      <c r="AY13" s="6"/>
       <c r="AZ13" s="1"/>
-      <c r="BA13" s="6"/>
-      <c r="BB13" s="6"/>
-      <c r="BC13" s="6"/>
-      <c r="BD13" s="6"/>
       <c r="BE13" s="1"/>
       <c r="BF13" s="1"/>
       <c r="BG13" s="1"/>
-      <c r="BH13" s="6"/>
-      <c r="BI13" s="6"/>
-      <c r="BJ13" s="6"/>
       <c r="BK13" s="1"/>
-      <c r="BL13" s="6"/>
-      <c r="BM13" s="6"/>
       <c r="BN13" s="1"/>
-      <c r="BO13" s="6"/>
-      <c r="BP13" s="6"/>
-      <c r="BQ13" s="6"/>
-      <c r="BR13" s="6"/>
-      <c r="BS13" s="6"/>
-      <c r="BT13" s="6"/>
-      <c r="BU13" s="6"/>
-      <c r="BV13" s="6"/>
-      <c r="BW13" s="6"/>
-      <c r="BX13" s="6"/>
-      <c r="BY13" s="6"/>
-      <c r="BZ13" s="6"/>
-      <c r="CA13" s="6"/>
-      <c r="CB13" s="6"/>
-      <c r="CC13" s="6"/>
-      <c r="CD13" s="6"/>
-      <c r="CE13" s="6"/>
-      <c r="CF13" s="6"/>
-      <c r="CG13" s="6"/>
-      <c r="CH13" s="6"/>
-      <c r="CI13" s="6"/>
-      <c r="CJ13" s="6"/>
-      <c r="CK13" s="6"/>
-      <c r="CL13" s="6"/>
       <c r="CM13" s="1"/>
-      <c r="CN13" s="6"/>
       <c r="CO13" s="1"/>
-      <c r="CP13" s="6"/>
       <c r="CQ13" s="1"/>
-      <c r="CR13" s="6"/>
       <c r="CS13" s="1"/>
-      <c r="CT13" s="6"/>
       <c r="CU13" s="1"/>
-      <c r="CV13" s="6"/>
       <c r="CW13" s="1"/>
-      <c r="CX13" s="6"/>
       <c r="CY13" s="1"/>
-      <c r="CZ13" s="6"/>
       <c r="DA13" s="1"/>
-      <c r="DB13" s="6"/>
       <c r="DC13" s="1"/>
-      <c r="DD13" s="6"/>
       <c r="DE13" s="1"/>
-      <c r="DF13" s="6"/>
-      <c r="DG13" s="6"/>
       <c r="DH13" s="1"/>
-      <c r="DI13" s="6"/>
-      <c r="DJ13" s="6"/>
       <c r="DK13" s="1"/>
-      <c r="DL13" s="6"/>
       <c r="DM13" s="1"/>
-      <c r="DN13" s="6"/>
       <c r="DO13" s="1"/>
-      <c r="DP13" s="6"/>
       <c r="DQ13" s="1"/>
-      <c r="DR13" s="6"/>
       <c r="DS13" s="1"/>
-      <c r="DT13" s="6"/>
       <c r="DU13" s="1"/>
-      <c r="DV13" s="6"/>
       <c r="DW13" s="1"/>
-      <c r="DX13" s="6"/>
       <c r="DY13" s="1"/>
-      <c r="DZ13" s="6"/>
       <c r="EA13" s="1"/>
-      <c r="EB13" s="6"/>
       <c r="EC13" s="1"/>
-      <c r="ED13" s="6"/>
       <c r="EE13" s="1"/>
-      <c r="EF13" s="6"/>
-      <c r="EG13" s="6"/>
       <c r="EH13" s="1"/>
-      <c r="EI13" s="6"/>
-      <c r="EJ13" s="6"/>
       <c r="EK13" s="1"/>
-      <c r="EL13" s="6"/>
       <c r="EM13" s="1"/>
-      <c r="EN13" s="6"/>
       <c r="EO13" s="1"/>
-      <c r="EP13" s="6"/>
       <c r="EQ13" s="1"/>
-      <c r="ER13" s="6"/>
       <c r="ES13" s="1"/>
-      <c r="ET13" s="6"/>
       <c r="EU13" s="1"/>
-      <c r="EV13" s="6"/>
-      <c r="EW13" s="6"/>
-      <c r="EX13" s="6"/>
-      <c r="EY13" s="6"/>
-      <c r="EZ13" s="6"/>
-      <c r="FA13" s="6"/>
-      <c r="FB13" s="6"/>
-      <c r="FC13" s="6"/>
-      <c r="FD13" s="6"/>
-      <c r="FE13" s="6"/>
-      <c r="FF13" s="6"/>
-      <c r="FG13" s="6"/>
-      <c r="FH13" s="6"/>
-      <c r="FI13" s="6"/>
-      <c r="FJ13" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="15.75">
-      <c r="A14" s="6"/>
+    </row>
+    <row r="14" spans="1:166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
       <c r="X14" s="1"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="6"/>
       <c r="AB14" s="1"/>
-      <c r="AC14" s="6"/>
       <c r="AD14" s="1"/>
-      <c r="AE14" s="6"/>
-      <c r="AF14" s="6"/>
-      <c r="AG14" s="6"/>
-      <c r="AH14" s="6"/>
-      <c r="AI14" s="6"/>
       <c r="AJ14" s="1"/>
-      <c r="AK14" s="6"/>
-      <c r="AL14" s="6"/>
       <c r="AM14" s="1"/>
-      <c r="AN14" s="6"/>
-      <c r="AO14" s="6"/>
-      <c r="AP14" s="6"/>
-      <c r="AQ14" s="6"/>
-      <c r="AR14" s="6"/>
       <c r="AS14" s="1"/>
-      <c r="AT14" s="6"/>
       <c r="AU14" s="1"/>
-      <c r="AV14" s="6"/>
-      <c r="AW14" s="6"/>
-      <c r="AX14" s="6"/>
-      <c r="AY14" s="6"/>
       <c r="AZ14" s="1"/>
-      <c r="BA14" s="6"/>
-      <c r="BB14" s="6"/>
-      <c r="BC14" s="6"/>
-      <c r="BD14" s="6"/>
       <c r="BE14" s="1"/>
       <c r="BF14" s="1"/>
       <c r="BG14" s="1"/>
-      <c r="BH14" s="6"/>
-      <c r="BI14" s="6"/>
-      <c r="BJ14" s="6"/>
       <c r="BK14" s="1"/>
-      <c r="BL14" s="6"/>
-      <c r="BM14" s="6"/>
       <c r="BN14" s="1"/>
-      <c r="BO14" s="6"/>
-      <c r="BP14" s="6"/>
-      <c r="BQ14" s="6"/>
-      <c r="BR14" s="6"/>
-      <c r="BS14" s="6"/>
-      <c r="BT14" s="6"/>
-      <c r="BU14" s="6"/>
-      <c r="BV14" s="6"/>
-      <c r="BW14" s="6"/>
-      <c r="BX14" s="6"/>
-      <c r="BY14" s="6"/>
-      <c r="BZ14" s="6"/>
-      <c r="CA14" s="6"/>
-      <c r="CB14" s="6"/>
-      <c r="CC14" s="6"/>
-      <c r="CD14" s="6"/>
-      <c r="CE14" s="6"/>
-      <c r="CF14" s="6"/>
-      <c r="CG14" s="6"/>
-      <c r="CH14" s="6"/>
-      <c r="CI14" s="6"/>
-      <c r="CJ14" s="6"/>
-      <c r="CK14" s="6"/>
-      <c r="CL14" s="6"/>
       <c r="CM14" s="1"/>
-      <c r="CN14" s="6"/>
       <c r="CO14" s="1"/>
-      <c r="CP14" s="6"/>
       <c r="CQ14" s="1"/>
-      <c r="CR14" s="6"/>
       <c r="CS14" s="1"/>
-      <c r="CT14" s="6"/>
       <c r="CU14" s="1"/>
-      <c r="CV14" s="6"/>
       <c r="CW14" s="1"/>
-      <c r="CX14" s="6"/>
       <c r="CY14" s="1"/>
-      <c r="CZ14" s="6"/>
       <c r="DA14" s="1"/>
-      <c r="DB14" s="6"/>
       <c r="DC14" s="1"/>
-      <c r="DD14" s="6"/>
       <c r="DE14" s="1"/>
-      <c r="DF14" s="6"/>
-      <c r="DG14" s="6"/>
       <c r="DH14" s="1"/>
-      <c r="DI14" s="6"/>
-      <c r="DJ14" s="6"/>
       <c r="DK14" s="1"/>
-      <c r="DL14" s="6"/>
       <c r="DM14" s="1"/>
-      <c r="DN14" s="6"/>
       <c r="DO14" s="1"/>
-      <c r="DP14" s="6"/>
       <c r="DQ14" s="1"/>
-      <c r="DR14" s="6"/>
       <c r="DS14" s="1"/>
-      <c r="DT14" s="6"/>
       <c r="DU14" s="1"/>
-      <c r="DV14" s="6"/>
       <c r="DW14" s="1"/>
-      <c r="DX14" s="6"/>
       <c r="DY14" s="1"/>
-      <c r="DZ14" s="6"/>
       <c r="EA14" s="1"/>
-      <c r="EB14" s="6"/>
       <c r="EC14" s="1"/>
-      <c r="ED14" s="6"/>
       <c r="EE14" s="1"/>
-      <c r="EF14" s="6"/>
-      <c r="EG14" s="6"/>
       <c r="EH14" s="1"/>
-      <c r="EI14" s="6"/>
-      <c r="EJ14" s="6"/>
       <c r="EK14" s="1"/>
-      <c r="EL14" s="6"/>
       <c r="EM14" s="1"/>
-      <c r="EN14" s="6"/>
       <c r="EO14" s="1"/>
-      <c r="EP14" s="6"/>
       <c r="EQ14" s="1"/>
-      <c r="ER14" s="6"/>
       <c r="ES14" s="1"/>
-      <c r="ET14" s="6"/>
       <c r="EU14" s="1"/>
-      <c r="EV14" s="6"/>
-      <c r="EW14" s="6"/>
-      <c r="EX14" s="6"/>
-      <c r="EY14" s="6"/>
-      <c r="EZ14" s="6"/>
-      <c r="FA14" s="6"/>
-      <c r="FB14" s="6"/>
-      <c r="FC14" s="6"/>
-      <c r="FD14" s="6"/>
-      <c r="FE14" s="6"/>
-      <c r="FF14" s="6"/>
-      <c r="FG14" s="6"/>
-      <c r="FH14" s="6"/>
-      <c r="FI14" s="6"/>
-      <c r="FJ14" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9907,51 +7858,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AI68"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="3" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="35" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="15.75">
+    <row r="1" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>25</v>
       </c>
@@ -9961,7 +7880,7 @@
       <c r="C1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -10054,7 +7973,7 @@
       <c r="AH1" s="5"/>
       <c r="AI1" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="15.75">
+    <row r="2" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>58</v>
       </c>
@@ -10064,7 +7983,7 @@
       <c r="C2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="7">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -10102,10 +8021,8 @@
       <c r="AE2" s="1"/>
       <c r="AF2" s="1"/>
       <c r="AG2" s="1"/>
-      <c r="AH2" s="6"/>
-      <c r="AI2" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="15.75">
+    </row>
+    <row r="3" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>64</v>
       </c>
@@ -10115,7 +8032,7 @@
       <c r="C3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="7">
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -10151,10 +8068,8 @@
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
       <c r="AG3" s="1"/>
-      <c r="AH3" s="6"/>
-      <c r="AI3" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="15.75">
+    </row>
+    <row r="4" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>69</v>
       </c>
@@ -10164,7 +8079,7 @@
       <c r="C4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="7">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -10200,10 +8115,8 @@
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="6"/>
-      <c r="AI4" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="15.75">
+    </row>
+    <row r="5" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>70</v>
       </c>
@@ -10213,7 +8126,7 @@
       <c r="C5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="7">
         <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -10255,10 +8168,8 @@
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
       <c r="AG5" s="1"/>
-      <c r="AH5" s="6"/>
-      <c r="AI5" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="15.75">
+    </row>
+    <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>76</v>
       </c>
@@ -10268,7 +8179,7 @@
       <c r="C6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="7">
         <v>6</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -10312,10 +8223,8 @@
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="15.75">
+    </row>
+    <row r="7" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>83</v>
       </c>
@@ -10325,7 +8234,7 @@
       <c r="C7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -10365,10 +8274,8 @@
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
       <c r="AG7" s="1"/>
-      <c r="AH7" s="6"/>
-      <c r="AI7" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="15.75">
+    </row>
+    <row r="8" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>88</v>
       </c>
@@ -10378,7 +8285,7 @@
       <c r="C8" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="7">
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -10426,10 +8333,8 @@
       <c r="AE8" s="1"/>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1"/>
-      <c r="AH8" s="6"/>
-      <c r="AI8" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="15.75">
+    </row>
+    <row r="9" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>97</v>
       </c>
@@ -10439,7 +8344,7 @@
       <c r="C9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="7">
         <v>2</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -10475,10 +8380,8 @@
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
       <c r="AG9" s="1"/>
-      <c r="AH9" s="6"/>
-      <c r="AI9" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="15.75">
+    </row>
+    <row r="10" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>98</v>
       </c>
@@ -10488,7 +8391,7 @@
       <c r="C10" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="7">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -10540,10 +8443,8 @@
       <c r="AE10" s="1"/>
       <c r="AF10" s="1"/>
       <c r="AG10" s="1"/>
-      <c r="AH10" s="6"/>
-      <c r="AI10" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="15.75">
+    </row>
+    <row r="11" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>109</v>
       </c>
@@ -10553,7 +8454,7 @@
       <c r="C11" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="7">
         <v>6</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -10597,10 +8498,8 @@
       <c r="AE11" s="1"/>
       <c r="AF11" s="1"/>
       <c r="AG11" s="1"/>
-      <c r="AH11" s="6"/>
-      <c r="AI11" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="15.75">
+    </row>
+    <row r="12" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>116</v>
       </c>
@@ -10610,7 +8509,7 @@
       <c r="C12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="7">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -10646,10 +8545,8 @@
       <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
       <c r="AG12" s="1"/>
-      <c r="AH12" s="6"/>
-      <c r="AI12" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="15.75">
+    </row>
+    <row r="13" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>117</v>
       </c>
@@ -10659,7 +8556,7 @@
       <c r="C13" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="7">
         <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -10705,10 +8602,8 @@
       <c r="AE13" s="1"/>
       <c r="AF13" s="1"/>
       <c r="AG13" s="1"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="15.75">
+    </row>
+    <row r="14" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>125</v>
       </c>
@@ -10718,7 +8613,7 @@
       <c r="C14" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="7">
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -10766,10 +8661,8 @@
       <c r="AE14" s="1"/>
       <c r="AF14" s="1"/>
       <c r="AG14" s="1"/>
-      <c r="AH14" s="6"/>
-      <c r="AI14" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="15.75">
+    </row>
+    <row r="15" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>134</v>
       </c>
@@ -10779,7 +8672,7 @@
       <c r="C15" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="7">
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -10819,10 +8712,8 @@
       <c r="AE15" s="1"/>
       <c r="AF15" s="1"/>
       <c r="AG15" s="1"/>
-      <c r="AH15" s="6"/>
-      <c r="AI15" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="15.75">
+    </row>
+    <row r="16" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>138</v>
       </c>
@@ -10832,7 +8723,7 @@
       <c r="C16" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="7">
         <v>6</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -10876,10 +8767,8 @@
       <c r="AE16" s="1"/>
       <c r="AF16" s="1"/>
       <c r="AG16" s="1"/>
-      <c r="AH16" s="6"/>
-      <c r="AI16" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="15.75">
+    </row>
+    <row r="17" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>139</v>
       </c>
@@ -10889,7 +8778,7 @@
       <c r="C17" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="7">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -10941,10 +8830,8 @@
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1"/>
-      <c r="AH17" s="6"/>
-      <c r="AI17" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="15.75">
+    </row>
+    <row r="18" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>140</v>
       </c>
@@ -10954,7 +8841,7 @@
       <c r="C18" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="7">
         <v>6</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -10998,10 +8885,8 @@
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1"/>
-      <c r="AH18" s="6"/>
-      <c r="AI18" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="15.75">
+    </row>
+    <row r="19" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>147</v>
       </c>
@@ -11011,7 +8896,7 @@
       <c r="C19" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="7">
         <v>7</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -11057,10 +8942,8 @@
       <c r="AE19" s="1"/>
       <c r="AF19" s="1"/>
       <c r="AG19" s="1"/>
-      <c r="AH19" s="6"/>
-      <c r="AI19" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="15.75">
+    </row>
+    <row r="20" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>155</v>
       </c>
@@ -11070,7 +8953,7 @@
       <c r="C20" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="7">
         <v>2</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -11106,10 +8989,8 @@
       <c r="AE20" s="1"/>
       <c r="AF20" s="1"/>
       <c r="AG20" s="1"/>
-      <c r="AH20" s="6"/>
-      <c r="AI20" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="15.75">
+    </row>
+    <row r="21" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>156</v>
       </c>
@@ -11119,7 +9000,7 @@
       <c r="C21" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="7">
         <v>3</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -11157,10 +9038,8 @@
       <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
       <c r="AG21" s="1"/>
-      <c r="AH21" s="6"/>
-      <c r="AI21" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="15.75">
+    </row>
+    <row r="22" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>160</v>
       </c>
@@ -11170,7 +9049,7 @@
       <c r="C22" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="7">
         <v>2</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -11206,10 +9085,8 @@
       <c r="AE22" s="1"/>
       <c r="AF22" s="1"/>
       <c r="AG22" s="1"/>
-      <c r="AH22" s="6"/>
-      <c r="AI22" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="15.75">
+    </row>
+    <row r="23" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>161</v>
       </c>
@@ -11219,7 +9096,7 @@
       <c r="C23" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="7">
         <v>2</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -11255,10 +9132,8 @@
       <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
       <c r="AG23" s="1"/>
-      <c r="AH23" s="6"/>
-      <c r="AI23" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="15.75">
+    </row>
+    <row r="24" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>162</v>
       </c>
@@ -11268,7 +9143,7 @@
       <c r="C24" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="7">
         <v>29</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -11358,10 +9233,8 @@
       <c r="AG24" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AH24" s="6"/>
-      <c r="AI24" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="15.75">
+    </row>
+    <row r="25" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>192</v>
       </c>
@@ -11371,7 +9244,7 @@
       <c r="C25" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="7">
         <v>6</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -11415,10 +9288,8 @@
       <c r="AE25" s="1"/>
       <c r="AF25" s="1"/>
       <c r="AG25" s="1"/>
-      <c r="AH25" s="6"/>
-      <c r="AI25" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="15.75">
+    </row>
+    <row r="26" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>199</v>
       </c>
@@ -11428,7 +9299,7 @@
       <c r="C26" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="7">
         <v>6</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -11472,10 +9343,8 @@
       <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
       <c r="AG26" s="1"/>
-      <c r="AH26" s="6"/>
-      <c r="AI26" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="15.75">
+    </row>
+    <row r="27" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>205</v>
       </c>
@@ -11485,7 +9354,7 @@
       <c r="C27" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="7">
         <v>5</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -11527,10 +9396,8 @@
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
       <c r="AG27" s="1"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="15.75">
+    </row>
+    <row r="28" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>211</v>
       </c>
@@ -11540,7 +9407,7 @@
       <c r="C28" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="7">
         <v>5</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -11582,10 +9449,8 @@
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
       <c r="AG28" s="1"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="15.75">
+    </row>
+    <row r="29" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>212</v>
       </c>
@@ -11595,7 +9460,7 @@
       <c r="C29" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="7">
         <v>5</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -11637,10 +9502,8 @@
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
       <c r="AG29" s="1"/>
-      <c r="AH29" s="6"/>
-      <c r="AI29" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="15.75">
+    </row>
+    <row r="30" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>218</v>
       </c>
@@ -11650,7 +9513,7 @@
       <c r="C30" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="7">
         <v>2</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -11686,10 +9549,8 @@
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
       <c r="AG30" s="1"/>
-      <c r="AH30" s="6"/>
-      <c r="AI30" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="15.75">
+    </row>
+    <row r="31" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>219</v>
       </c>
@@ -11699,7 +9560,7 @@
       <c r="C31" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="7">
         <v>2</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -11735,10 +9596,8 @@
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
       <c r="AG31" s="1"/>
-      <c r="AH31" s="6"/>
-      <c r="AI31" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="15.75">
+    </row>
+    <row r="32" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>220</v>
       </c>
@@ -11748,7 +9607,7 @@
       <c r="C32" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="7">
         <v>7</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -11794,10 +9653,8 @@
       <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
       <c r="AG32" s="1"/>
-      <c r="AH32" s="6"/>
-      <c r="AI32" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="15.75">
+    </row>
+    <row r="33" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>226</v>
       </c>
@@ -11807,7 +9664,7 @@
       <c r="C33" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="7">
         <v>5</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -11849,10 +9706,8 @@
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
       <c r="AG33" s="1"/>
-      <c r="AH33" s="6"/>
-      <c r="AI33" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="15.75">
+    </row>
+    <row r="34" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>232</v>
       </c>
@@ -11862,7 +9717,7 @@
       <c r="C34" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="7">
         <v>7</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -11908,10 +9763,8 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
       <c r="AG34" s="1"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="15.75">
+    </row>
+    <row r="35" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>233</v>
       </c>
@@ -11921,7 +9774,7 @@
       <c r="C35" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="7">
         <v>4</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -11961,10 +9814,8 @@
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
       <c r="AG35" s="1"/>
-      <c r="AH35" s="6"/>
-      <c r="AI35" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="15.75">
+    </row>
+    <row r="36" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>238</v>
       </c>
@@ -11974,7 +9825,7 @@
       <c r="C36" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="7">
         <v>2</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -12010,10 +9861,8 @@
       <c r="AE36" s="1"/>
       <c r="AF36" s="1"/>
       <c r="AG36" s="1"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="15.75">
+    </row>
+    <row r="37" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>239</v>
       </c>
@@ -12023,7 +9872,7 @@
       <c r="C37" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="7">
         <v>4</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -12063,10 +9912,8 @@
       <c r="AE37" s="1"/>
       <c r="AF37" s="1"/>
       <c r="AG37" s="1"/>
-      <c r="AH37" s="6"/>
-      <c r="AI37" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="15.75">
+    </row>
+    <row r="38" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>244</v>
       </c>
@@ -12076,7 +9923,7 @@
       <c r="C38" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="7">
         <v>16</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -12140,10 +9987,8 @@
       <c r="AE38" s="1"/>
       <c r="AF38" s="1"/>
       <c r="AG38" s="1"/>
-      <c r="AH38" s="6"/>
-      <c r="AI38" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="15.75">
+    </row>
+    <row r="39" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>261</v>
       </c>
@@ -12153,7 +9998,7 @@
       <c r="C39" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="7">
         <v>3</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -12191,10 +10036,8 @@
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
       <c r="AG39" s="1"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="15.75">
+    </row>
+    <row r="40" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>14</v>
       </c>
@@ -12204,7 +10047,7 @@
       <c r="C40" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="7">
         <v>4</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -12244,10 +10087,8 @@
       <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
       <c r="AG40" s="1"/>
-      <c r="AH40" s="6"/>
-      <c r="AI40" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="15.75">
+    </row>
+    <row r="41" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>268</v>
       </c>
@@ -12257,7 +10098,7 @@
       <c r="C41" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="7">
         <v>3</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -12295,10 +10136,8 @@
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
       <c r="AG41" s="1"/>
-      <c r="AH41" s="6"/>
-      <c r="AI41" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="15.75">
+    </row>
+    <row r="42" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>272</v>
       </c>
@@ -12308,7 +10147,7 @@
       <c r="C42" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="7">
         <v>3</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -12346,10 +10185,8 @@
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
       <c r="AG42" s="1"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="15.75">
+    </row>
+    <row r="43" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>276</v>
       </c>
@@ -12359,7 +10196,7 @@
       <c r="C43" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="7">
         <v>3</v>
       </c>
       <c r="E43" s="1" t="s">
@@ -12397,10 +10234,8 @@
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
       <c r="AG43" s="1"/>
-      <c r="AH43" s="6"/>
-      <c r="AI43" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="15.75">
+    </row>
+    <row r="44" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>280</v>
       </c>
@@ -12410,7 +10245,7 @@
       <c r="C44" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="7">
         <v>5</v>
       </c>
       <c r="E44" s="1" t="s">
@@ -12452,10 +10287,8 @@
       <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
       <c r="AG44" s="1"/>
-      <c r="AH44" s="6"/>
-      <c r="AI44" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="15.75">
+    </row>
+    <row r="45" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>286</v>
       </c>
@@ -12465,7 +10298,7 @@
       <c r="C45" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="7">
         <v>8</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -12513,10 +10346,8 @@
       <c r="AE45" s="1"/>
       <c r="AF45" s="1"/>
       <c r="AG45" s="1"/>
-      <c r="AH45" s="6"/>
-      <c r="AI45" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="15.75">
+    </row>
+    <row r="46" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>295</v>
       </c>
@@ -12526,7 +10357,7 @@
       <c r="C46" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="7">
         <v>4</v>
       </c>
       <c r="E46" s="1" t="s">
@@ -12566,10 +10397,8 @@
       <c r="AE46" s="1"/>
       <c r="AF46" s="1"/>
       <c r="AG46" s="1"/>
-      <c r="AH46" s="6"/>
-      <c r="AI46" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="15.75">
+    </row>
+    <row r="47" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>297</v>
       </c>
@@ -12579,7 +10408,7 @@
       <c r="C47" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="7">
         <v>4</v>
       </c>
       <c r="E47" s="1" t="s">
@@ -12619,10 +10448,8 @@
       <c r="AE47" s="1"/>
       <c r="AF47" s="1"/>
       <c r="AG47" s="1"/>
-      <c r="AH47" s="6"/>
-      <c r="AI47" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="15.75">
+    </row>
+    <row r="48" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>302</v>
       </c>
@@ -12632,7 +10459,7 @@
       <c r="C48" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="7">
         <v>4</v>
       </c>
       <c r="E48" s="1" t="s">
@@ -12672,10 +10499,8 @@
       <c r="AE48" s="1"/>
       <c r="AF48" s="1"/>
       <c r="AG48" s="1"/>
-      <c r="AH48" s="6"/>
-      <c r="AI48" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="15.75">
+    </row>
+    <row r="49" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>303</v>
       </c>
@@ -12685,7 +10510,7 @@
       <c r="C49" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="7">
         <v>13</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -12743,10 +10568,8 @@
       <c r="AE49" s="1"/>
       <c r="AF49" s="1"/>
       <c r="AG49" s="1"/>
-      <c r="AH49" s="6"/>
-      <c r="AI49" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="15.75">
+    </row>
+    <row r="50" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>317</v>
       </c>
@@ -12756,7 +10579,7 @@
       <c r="C50" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="7">
         <v>13</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -12814,10 +10637,8 @@
       <c r="AE50" s="1"/>
       <c r="AF50" s="1"/>
       <c r="AG50" s="1"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="15.75">
+    </row>
+    <row r="51" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>318</v>
       </c>
@@ -12827,7 +10648,7 @@
       <c r="C51" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="7">
         <v>13</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -12885,10 +10706,8 @@
       <c r="AE51" s="1"/>
       <c r="AF51" s="1"/>
       <c r="AG51" s="1"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="15.75">
+    </row>
+    <row r="52" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>319</v>
       </c>
@@ -12898,7 +10717,7 @@
       <c r="C52" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="7">
         <v>13</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -12956,10 +10775,8 @@
       <c r="AE52" s="1"/>
       <c r="AF52" s="1"/>
       <c r="AG52" s="1"/>
-      <c r="AH52" s="6"/>
-      <c r="AI52" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="15.75">
+    </row>
+    <row r="53" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>320</v>
       </c>
@@ -12969,7 +10786,7 @@
       <c r="C53" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="7">
         <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
@@ -13031,10 +10848,8 @@
       <c r="AE53" s="1"/>
       <c r="AF53" s="1"/>
       <c r="AG53" s="1"/>
-      <c r="AH53" s="6"/>
-      <c r="AI53" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="15.75">
+    </row>
+    <row r="54" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>323</v>
       </c>
@@ -13044,7 +10859,7 @@
       <c r="C54" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="7">
         <v>13</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -13102,10 +10917,8 @@
       <c r="AE54" s="1"/>
       <c r="AF54" s="1"/>
       <c r="AG54" s="1"/>
-      <c r="AH54" s="6"/>
-      <c r="AI54" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="15.75">
+    </row>
+    <row r="55" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>324</v>
       </c>
@@ -13115,7 +10928,7 @@
       <c r="C55" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="7">
         <v>13</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -13173,10 +10986,8 @@
       <c r="AE55" s="1"/>
       <c r="AF55" s="1"/>
       <c r="AG55" s="1"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="15.75">
+    </row>
+    <row r="56" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>325</v>
       </c>
@@ -13186,7 +10997,7 @@
       <c r="C56" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="7">
         <v>13</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -13244,10 +11055,8 @@
       <c r="AE56" s="1"/>
       <c r="AF56" s="1"/>
       <c r="AG56" s="1"/>
-      <c r="AH56" s="6"/>
-      <c r="AI56" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="15.75">
+    </row>
+    <row r="57" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>326</v>
       </c>
@@ -13257,7 +11066,7 @@
       <c r="C57" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="7">
         <v>13</v>
       </c>
       <c r="E57" s="1" t="s">
@@ -13315,10 +11124,8 @@
       <c r="AE57" s="1"/>
       <c r="AF57" s="1"/>
       <c r="AG57" s="1"/>
-      <c r="AH57" s="6"/>
-      <c r="AI57" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
+    </row>
+    <row r="58" spans="1:33" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>327</v>
       </c>
@@ -13328,7 +11135,7 @@
       <c r="C58" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="7">
         <v>13</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -13386,10 +11193,8 @@
       <c r="AE58" s="1"/>
       <c r="AF58" s="1"/>
       <c r="AG58" s="1"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
+    </row>
+    <row r="59" spans="1:33" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>328</v>
       </c>
@@ -13399,7 +11204,7 @@
       <c r="C59" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D59" s="7">
         <v>13</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -13457,10 +11262,8 @@
       <c r="AE59" s="1"/>
       <c r="AF59" s="1"/>
       <c r="AG59" s="1"/>
-      <c r="AH59" s="6"/>
-      <c r="AI59" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
+    </row>
+    <row r="60" spans="1:33" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>329</v>
       </c>
@@ -13470,7 +11273,7 @@
       <c r="C60" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="7">
         <v>13</v>
       </c>
       <c r="E60" s="1" t="s">
@@ -13528,10 +11331,8 @@
       <c r="AE60" s="1"/>
       <c r="AF60" s="1"/>
       <c r="AG60" s="1"/>
-      <c r="AH60" s="6"/>
-      <c r="AI60" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
+    </row>
+    <row r="61" spans="1:33" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>330</v>
       </c>
@@ -13541,7 +11342,7 @@
       <c r="C61" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D61" s="7">
         <v>13</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -13599,10 +11400,8 @@
       <c r="AE61" s="1"/>
       <c r="AF61" s="1"/>
       <c r="AG61" s="1"/>
-      <c r="AH61" s="6"/>
-      <c r="AI61" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
+    </row>
+    <row r="62" spans="1:33" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>331</v>
       </c>
@@ -13612,7 +11411,7 @@
       <c r="C62" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D62" s="9">
+      <c r="D62" s="7">
         <v>13</v>
       </c>
       <c r="E62" s="1" t="s">
@@ -13670,10 +11469,8 @@
       <c r="AE62" s="1"/>
       <c r="AF62" s="1"/>
       <c r="AG62" s="1"/>
-      <c r="AH62" s="6"/>
-      <c r="AI62" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
+    </row>
+    <row r="63" spans="1:33" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>332</v>
       </c>
@@ -13683,7 +11480,7 @@
       <c r="C63" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D63" s="9">
+      <c r="D63" s="7">
         <v>13</v>
       </c>
       <c r="E63" s="1" t="s">
@@ -13741,10 +11538,8 @@
       <c r="AE63" s="1"/>
       <c r="AF63" s="1"/>
       <c r="AG63" s="1"/>
-      <c r="AH63" s="6"/>
-      <c r="AI63" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
+    </row>
+    <row r="64" spans="1:33" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>333</v>
       </c>
@@ -13754,7 +11549,7 @@
       <c r="C64" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D64" s="9">
+      <c r="D64" s="7">
         <v>13</v>
       </c>
       <c r="E64" s="1" t="s">
@@ -13812,10 +11607,8 @@
       <c r="AE64" s="1"/>
       <c r="AF64" s="1"/>
       <c r="AG64" s="1"/>
-      <c r="AH64" s="6"/>
-      <c r="AI64" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
+    </row>
+    <row r="65" spans="1:33" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>334</v>
       </c>
@@ -13825,7 +11618,7 @@
       <c r="C65" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D65" s="9">
+      <c r="D65" s="7">
         <v>13</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -13883,10 +11676,8 @@
       <c r="AE65" s="1"/>
       <c r="AF65" s="1"/>
       <c r="AG65" s="1"/>
-      <c r="AH65" s="6"/>
-      <c r="AI65" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
+    </row>
+    <row r="66" spans="1:33" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>335</v>
       </c>
@@ -13896,7 +11687,7 @@
       <c r="C66" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="7">
         <v>13</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -13954,10 +11745,8 @@
       <c r="AE66" s="1"/>
       <c r="AF66" s="1"/>
       <c r="AG66" s="1"/>
-      <c r="AH66" s="6"/>
-      <c r="AI66" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
+    </row>
+    <row r="67" spans="1:33" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>336</v>
       </c>
@@ -13967,7 +11756,7 @@
       <c r="C67" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D67" s="9">
+      <c r="D67" s="7">
         <v>13</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -14025,10 +11814,8 @@
       <c r="AE67" s="1"/>
       <c r="AF67" s="1"/>
       <c r="AG67" s="1"/>
-      <c r="AH67" s="6"/>
-      <c r="AI67" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
+    </row>
+    <row r="68" spans="1:33" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>337</v>
       </c>
@@ -14038,7 +11825,7 @@
       <c r="C68" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="7">
         <v>13</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -14096,8 +11883,6 @@
       <c r="AE68" s="1"/>
       <c r="AF68" s="1"/>
       <c r="AG68" s="1"/>
-      <c r="AH68" s="6"/>
-      <c r="AI68" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14105,33 +11890,17 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="17" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="15.75">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14184,7 +11953,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="15.75">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -14237,7 +12006,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="15.75">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
@@ -14290,195 +12059,35 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="15.75">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G4" s="1"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="15.75">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+    </row>
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G5" s="1"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="15.75">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
+    </row>
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G6" s="1"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="15.75">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+    </row>
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G7" s="1"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="15.75">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+    </row>
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G8" s="1"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="15.75">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+    </row>
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G9" s="1"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="15.75">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+    </row>
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G10" s="1"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="15.75">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+    </row>
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G11" s="1"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="15.75">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+    </row>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G12" s="1"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="15.75">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+    </row>
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G13" s="1"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
